--- a/VERGARA/Septiembre/vergara Septiembre.xlsx
+++ b/VERGARA/Septiembre/vergara Septiembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\VERGARA\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\VERGARA\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72987526-886D-4F54-B648-2AFFFA2A03E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8272EEC8-8102-4E18-B3CF-D8B71C5213D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -790,12 +790,6 @@
     <t>QUIENES ESTAN MARCADO DE COLOR ROJO NO ESTAN RESPETANDO LOS CENTAVOS AL ABONAR</t>
   </si>
   <si>
-    <t>EL MES PASADO PAGO BIEN EL 08/07  $145.692,44 Y LA PUSIMOS NO PAGA</t>
-  </si>
-  <si>
-    <t>SE QUEJA POR MAIL DE DEUDA INEXISTENTE Y ADJUNTA COMPROBANTES</t>
-  </si>
-  <si>
     <t>Debito 01/09</t>
   </si>
   <si>
@@ -860,6 +854,12 @@
   </si>
   <si>
     <t>QUIENES POSEAN UNIDADES FUNCIONALES MARCADAS EN VERDES PORFAVOR ABONAR ANTES DEL PRIMER VENCIMIENTO.</t>
+  </si>
+  <si>
+    <t>Leer la anotacion</t>
+  </si>
+  <si>
+    <t>EL MES PASADO PAGO BIEN  Y NO LO PUSIMOS PAGO - HABIA ABONADO $111.067,79 - Este mes debe abonar  $117.783,79</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1072,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1147,12 +1147,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1659,7 +1653,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="272">
+  <cellXfs count="283">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1887,7 +1881,6 @@
     </xf>
     <xf numFmtId="44" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1901,26 +1894,26 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="19" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="14" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="14" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="14" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="19" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="13" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="13" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="13" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="13" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="19" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="19" fillId="13" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="25" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1929,34 +1922,61 @@
     </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="19" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="19" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="14" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="14" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="14" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="14" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1973,74 +1993,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="3" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2077,29 +2041,74 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="3" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="19" fillId="15" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="19" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="15" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="15" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="15" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="14" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="44" fontId="19" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="19" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="12" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="12" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="12" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2461,20 +2470,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M103"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
       <c r="B1" s="64" t="s">
         <v>0</v>
@@ -2483,7 +2492,7 @@
       <c r="D1" s="64"/>
       <c r="E1" s="65"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="125" t="s">
         <v>1</v>
@@ -2492,7 +2501,7 @@
       <c r="D2" s="125"/>
       <c r="E2" s="66"/>
     </row>
-    <row r="3" spans="1:5" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15"/>
       <c r="B3" s="126" t="s">
         <v>2</v>
@@ -2503,7 +2512,7 @@
       </c>
       <c r="E3" s="66"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
@@ -2514,18 +2523,18 @@
       <c r="D4" s="17"/>
       <c r="E4" s="18"/>
     </row>
-    <row r="5" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="193" t="s">
-        <v>257</v>
-      </c>
-      <c r="C5" s="194"/>
-      <c r="D5" s="194"/>
-      <c r="E5" s="195"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="233" t="s">
+        <v>255</v>
+      </c>
+      <c r="C5" s="225"/>
+      <c r="D5" s="225"/>
+      <c r="E5" s="226"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
@@ -2536,57 +2545,57 @@
       </c>
       <c r="E6" s="18"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="196" t="s">
-        <v>256</v>
-      </c>
-      <c r="C8" s="197"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="197"/>
-      <c r="C9" s="197"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="197"/>
-      <c r="C10" s="197"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="198" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="234" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" s="220"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="220"/>
+      <c r="C9" s="220"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="220"/>
+      <c r="C10" s="220"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="235" t="s">
         <v>249</v>
       </c>
-      <c r="B13" s="199"/>
-      <c r="C13" s="199"/>
-      <c r="D13" s="199"/>
-      <c r="E13" s="199"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="199"/>
-      <c r="B14" s="199"/>
-      <c r="C14" s="199"/>
-      <c r="D14" s="199"/>
-      <c r="E14" s="199"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="199"/>
-      <c r="B15" s="199"/>
-      <c r="C15" s="199"/>
-      <c r="D15" s="199"/>
-      <c r="E15" s="199"/>
-    </row>
-    <row r="16" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="199"/>
-      <c r="B16" s="199"/>
-      <c r="C16" s="199"/>
-      <c r="D16" s="199"/>
-      <c r="E16" s="199"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="236"/>
+      <c r="C13" s="236"/>
+      <c r="D13" s="236"/>
+      <c r="E13" s="236"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="236"/>
+      <c r="B14" s="236"/>
+      <c r="C14" s="236"/>
+      <c r="D14" s="236"/>
+      <c r="E14" s="236"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="236"/>
+      <c r="B15" s="236"/>
+      <c r="C15" s="236"/>
+      <c r="D15" s="236"/>
+      <c r="E15" s="236"/>
+    </row>
+    <row r="16" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="236"/>
+      <c r="B16" s="236"/>
+      <c r="C16" s="236"/>
+      <c r="D16" s="236"/>
+      <c r="E16" s="236"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>9</v>
       </c>
@@ -2595,7 +2604,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="32" t="s">
         <v>10</v>
       </c>
@@ -2604,42 +2613,42 @@
       <c r="D21" s="30"/>
       <c r="E21" s="30"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="188">
+      <c r="D22" s="187">
         <v>689879.8</v>
       </c>
       <c r="E22" s="84"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="188">
+      <c r="D23" s="187">
         <v>-158358.17000000001</v>
       </c>
       <c r="E23" s="84"/>
       <c r="G23" s="19"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="188">
+      <c r="D24" s="187">
         <v>0.37</v>
       </c>
       <c r="E24" s="84"/>
       <c r="G24" s="19"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="55" t="s">
         <v>14</v>
       </c>
@@ -2652,15 +2661,15 @@
       <c r="E25" s="85"/>
       <c r="G25" s="19"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="52"/>
-      <c r="B26" s="167"/>
-      <c r="C26" s="167"/>
-      <c r="D26" s="189"/>
-      <c r="E26" s="168"/>
+      <c r="B26" s="166"/>
+      <c r="C26" s="166"/>
+      <c r="D26" s="188"/>
+      <c r="E26" s="167"/>
       <c r="G26" s="19"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="55" t="s">
         <v>14</v>
       </c>
@@ -2673,7 +2682,7 @@
       <c r="E27" s="85"/>
       <c r="G27" s="19"/>
     </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="51" t="s">
         <v>15</v>
       </c>
@@ -2686,7 +2695,7 @@
       </c>
       <c r="F28" s="19"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="32" t="s">
         <v>16</v>
       </c>
@@ -2695,34 +2704,34 @@
       <c r="D29" s="33"/>
       <c r="E29" s="87"/>
     </row>
-    <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="200" t="s">
+    <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="221" t="s">
+        <v>256</v>
+      </c>
+      <c r="B30" s="222"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="187">
+        <v>40000</v>
+      </c>
+      <c r="E30" s="138" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="221" t="s">
         <v>258</v>
       </c>
-      <c r="B30" s="201"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="188">
-        <v>40000</v>
-      </c>
-      <c r="E30" s="138" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="200" t="s">
-        <v>260</v>
-      </c>
-      <c r="B31" s="201"/>
+      <c r="B31" s="222"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="188">
+      <c r="D31" s="187">
         <f>470000</f>
         <v>470000</v>
       </c>
       <c r="E31" s="138" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="25" t="s">
         <v>17</v>
       </c>
@@ -2734,7 +2743,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="30" t="s">
         <v>18</v>
       </c>
@@ -2743,32 +2752,32 @@
       <c r="D33" s="34"/>
       <c r="E33" s="63"/>
     </row>
-    <row r="34" spans="1:7" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="140" t="s">
         <v>19</v>
       </c>
       <c r="B34" s="137"/>
       <c r="C34" s="53"/>
-      <c r="D34" s="190">
+      <c r="D34" s="189">
         <v>70868</v>
       </c>
       <c r="E34" s="96" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G34" s="139"/>
     </row>
-    <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="200" t="s">
+    <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="221" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="201"/>
+      <c r="B35" s="222"/>
       <c r="C35" s="53"/>
-      <c r="D35" s="191">
+      <c r="D35" s="190">
         <v>719.9</v>
       </c>
       <c r="E35" s="110"/>
     </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="25" t="s">
         <v>21</v>
       </c>
@@ -2780,7 +2789,7 @@
         <v>71587.899999999994</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="32" t="s">
         <v>22</v>
       </c>
@@ -2789,36 +2798,36 @@
       <c r="D37" s="37"/>
       <c r="E37" s="90"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="52"/>
-      <c r="D38" s="192">
+      <c r="D38" s="191">
         <v>309430.93</v>
       </c>
       <c r="E38" s="112" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G38" s="116"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="5"/>
-      <c r="D39" s="191">
+      <c r="D39" s="190">
         <v>27933.97</v>
       </c>
       <c r="E39" s="98" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="str">
         <f>A39</f>
         <v>Sindicatos mes de SEPTIEMBRE</v>
@@ -2827,7 +2836,7 @@
         <v>25</v>
       </c>
       <c r="C40" s="5"/>
-      <c r="D40" s="191">
+      <c r="D40" s="190">
         <v>52835.06</v>
       </c>
       <c r="E40" s="98" t="str">
@@ -2835,7 +2844,7 @@
         <v>Debito 12/09</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="str">
         <f>A40</f>
         <v>Sindicatos mes de SEPTIEMBRE</v>
@@ -2844,7 +2853,7 @@
         <v>26</v>
       </c>
       <c r="C41" s="5"/>
-      <c r="D41" s="191">
+      <c r="D41" s="190">
         <v>3103.67</v>
       </c>
       <c r="E41" s="99" t="str">
@@ -2852,7 +2861,7 @@
         <v>Debito 12/09</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="25" t="s">
         <v>27</v>
       </c>
@@ -2864,7 +2873,7 @@
         <v>393303.63</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="32" t="s">
         <v>28</v>
       </c>
@@ -2873,46 +2882,46 @@
       <c r="D43" s="37"/>
       <c r="E43" s="90"/>
     </row>
-    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B44" s="52"/>
       <c r="C44" s="52"/>
-      <c r="D44" s="191">
+      <c r="D44" s="190">
         <v>1397945.12</v>
       </c>
       <c r="E44" s="96" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
-      <c r="D45" s="191">
+      <c r="D45" s="190">
         <v>50000</v>
       </c>
-      <c r="E45" s="166" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="200" t="s">
+      <c r="E45" s="165" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="221" t="s">
         <v>31</v>
       </c>
-      <c r="B46" s="201"/>
+      <c r="B46" s="222"/>
       <c r="C46" s="5"/>
-      <c r="D46" s="191">
+      <c r="D46" s="190">
         <v>92637</v>
       </c>
       <c r="E46" s="96" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="25" t="s">
         <v>32</v>
       </c>
@@ -2924,7 +2933,7 @@
         <v>1540582.12</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="32" t="s">
         <v>33</v>
       </c>
@@ -2933,105 +2942,105 @@
       <c r="D48" s="36"/>
       <c r="E48" s="92"/>
     </row>
-    <row r="49" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="209" t="s">
-        <v>272</v>
-      </c>
-      <c r="B49" s="210"/>
+    <row r="49" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="231" t="s">
+        <v>270</v>
+      </c>
+      <c r="B49" s="232"/>
       <c r="C49" s="54"/>
-      <c r="D49" s="191">
+      <c r="D49" s="190">
         <v>119856.78</v>
       </c>
-      <c r="E49" s="166" t="s">
-        <v>273</v>
+      <c r="E49" s="165" t="s">
+        <v>271</v>
       </c>
       <c r="H49" s="116"/>
     </row>
-    <row r="50" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="169" t="s">
-        <v>271</v>
-      </c>
-      <c r="B50" s="170"/>
+    <row r="50" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="168" t="s">
+        <v>269</v>
+      </c>
+      <c r="B50" s="169"/>
       <c r="C50" s="54"/>
-      <c r="D50" s="191">
+      <c r="D50" s="190">
         <f>71000+84130</f>
         <v>155130</v>
       </c>
-      <c r="E50" s="166" t="s">
+      <c r="E50" s="165" t="s">
+        <v>266</v>
+      </c>
+      <c r="H50" s="116"/>
+    </row>
+    <row r="51" spans="1:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="229" t="s">
+        <v>265</v>
+      </c>
+      <c r="B51" s="230"/>
+      <c r="C51" s="54"/>
+      <c r="D51" s="190">
+        <v>168400</v>
+      </c>
+      <c r="E51" s="165" t="s">
+        <v>266</v>
+      </c>
+      <c r="H51" s="116"/>
+    </row>
+    <row r="52" spans="1:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="93" t="s">
         <v>268</v>
-      </c>
-      <c r="H50" s="116"/>
-    </row>
-    <row r="51" spans="1:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="207" t="s">
-        <v>267</v>
-      </c>
-      <c r="B51" s="208"/>
-      <c r="C51" s="54"/>
-      <c r="D51" s="191">
-        <v>168400</v>
-      </c>
-      <c r="E51" s="166" t="s">
-        <v>268</v>
-      </c>
-      <c r="H51" s="116"/>
-    </row>
-    <row r="52" spans="1:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="93" t="s">
-        <v>270</v>
       </c>
       <c r="B52" s="137"/>
       <c r="C52" s="54"/>
-      <c r="D52" s="191">
+      <c r="D52" s="190">
         <v>120000</v>
       </c>
-      <c r="E52" s="166" t="s">
-        <v>268</v>
+      <c r="E52" s="165" t="s">
+        <v>266</v>
       </c>
       <c r="H52" s="116"/>
     </row>
-    <row r="53" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="169" t="s">
-        <v>266</v>
-      </c>
-      <c r="B53" s="170"/>
+    <row r="53" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="168" t="s">
+        <v>264</v>
+      </c>
+      <c r="B53" s="169"/>
       <c r="C53" s="54"/>
-      <c r="D53" s="191">
+      <c r="D53" s="190">
         <v>120000</v>
       </c>
       <c r="E53" s="138" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H53" s="116"/>
     </row>
-    <row r="54" spans="1:10" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="205" t="s">
-        <v>264</v>
-      </c>
-      <c r="B54" s="206"/>
+    <row r="54" spans="1:10" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="227" t="s">
+        <v>262</v>
+      </c>
+      <c r="B54" s="228"/>
       <c r="C54" s="52"/>
       <c r="D54" s="94">
         <v>150000</v>
       </c>
       <c r="E54" s="138" t="s">
-        <v>265</v>
-      </c>
-      <c r="I54" s="200"/>
-      <c r="J54" s="201"/>
-    </row>
-    <row r="55" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>263</v>
+      </c>
+      <c r="I54" s="221"/>
+      <c r="J54" s="222"/>
+    </row>
+    <row r="55" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="25" t="s">
         <v>34</v>
       </c>
       <c r="B55" s="32"/>
       <c r="C55" s="32"/>
       <c r="D55" s="30"/>
-      <c r="E55" s="171">
+      <c r="E55" s="170">
         <f>SUM(D49:D54)</f>
         <v>833386.78</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="32" t="s">
         <v>35</v>
       </c>
@@ -3040,29 +3049,29 @@
       <c r="D56" s="27"/>
       <c r="E56" s="92"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="191">
+      <c r="D57" s="190">
         <v>104362.68</v>
       </c>
       <c r="E57" s="100"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="191">
+      <c r="D58" s="190">
         <v>56000</v>
       </c>
       <c r="E58" s="97"/>
     </row>
-    <row r="59" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="51" t="s">
         <v>17</v>
       </c>
@@ -3074,14 +3083,14 @@
         <v>160362.68</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="84"/>
       <c r="E60" s="102"/>
     </row>
-    <row r="61" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="28" t="s">
         <v>38</v>
       </c>
@@ -3090,35 +3099,35 @@
       <c r="D61" s="103"/>
       <c r="E61" s="130"/>
     </row>
-    <row r="62" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1"/>
       <c r="D62" s="104"/>
       <c r="E62" s="105"/>
       <c r="F62" s="44"/>
       <c r="G62" s="133"/>
     </row>
-    <row r="63" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B63" s="9"/>
       <c r="C63" s="4"/>
       <c r="D63" s="106"/>
-      <c r="E63" s="184">
+      <c r="E63" s="183">
         <f>(SUM(E28:E61))</f>
         <v>4040745.11</v>
       </c>
       <c r="F63" s="129"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D64" s="104"/>
       <c r="E64" s="104"/>
     </row>
-    <row r="65" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D65" s="104"/>
       <c r="E65" s="104"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="10" t="s">
         <v>40</v>
       </c>
@@ -3127,21 +3136,21 @@
       <c r="D66" s="107"/>
       <c r="E66" s="108"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="200"/>
-      <c r="B67" s="201"/>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="221"/>
+      <c r="B67" s="222"/>
       <c r="C67" s="5"/>
       <c r="D67" s="94"/>
       <c r="E67" s="91"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="93"/>
       <c r="B68" s="95"/>
       <c r="C68" s="5"/>
       <c r="D68" s="94"/>
       <c r="E68" s="91"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="49"/>
       <c r="B69" s="48"/>
       <c r="C69" s="48"/>
@@ -3151,19 +3160,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="71" spans="1:5" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="72" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="204" t="s">
+    <row r="70" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="71" spans="1:5" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="72" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="224" t="s">
         <v>41</v>
       </c>
-      <c r="B72" s="194"/>
-      <c r="C72" s="194"/>
-      <c r="D72" s="195"/>
+      <c r="B72" s="225"/>
+      <c r="C72" s="225"/>
+      <c r="D72" s="226"/>
       <c r="E72" s="134"/>
     </row>
-    <row r="73" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="74" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="74" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>42</v>
       </c>
@@ -3175,8 +3184,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="76" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="81" t="s">
         <v>43</v>
       </c>
@@ -3185,7 +3194,7 @@
         <v>4040745.11</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="81" t="s">
         <v>44</v>
       </c>
@@ -3194,7 +3203,7 @@
         <v>4040745.11</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="81" t="s">
         <v>45</v>
       </c>
@@ -3203,7 +3212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="81" t="s">
         <v>46</v>
       </c>
@@ -3212,15 +3221,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="45" t="s">
         <v>47</v>
       </c>
       <c r="B81" s="117"/>
       <c r="C81" s="20"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="29" t="s">
         <v>48</v>
       </c>
@@ -3229,7 +3238,7 @@
       </c>
       <c r="C82" s="22"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="21" t="s">
         <v>49</v>
       </c>
@@ -3239,7 +3248,7 @@
       </c>
       <c r="C83" s="20"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="21" t="s">
         <v>50</v>
       </c>
@@ -3249,14 +3258,14 @@
       </c>
       <c r="C84" s="20"/>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="113" t="s">
         <v>51</v>
       </c>
       <c r="B85" s="47"/>
       <c r="C85" s="20"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="40" t="s">
         <v>52</v>
       </c>
@@ -3266,7 +3275,7 @@
       </c>
       <c r="C86" s="20"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="40" t="s">
         <v>53</v>
       </c>
@@ -3276,7 +3285,7 @@
       </c>
       <c r="C87" s="20"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="40" t="s">
         <v>54</v>
       </c>
@@ -3286,7 +3295,7 @@
       </c>
       <c r="C88" s="20"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="24" t="s">
         <v>55</v>
       </c>
@@ -3296,7 +3305,7 @@
       </c>
       <c r="C89" s="20"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="120" t="s">
         <v>34</v>
       </c>
@@ -3307,52 +3316,52 @@
       <c r="C90" s="23"/>
       <c r="D90" s="44"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B91" s="42"/>
       <c r="C91" s="23"/>
       <c r="D91" s="44"/>
       <c r="E91" s="118"/>
       <c r="F91" s="119"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B92" s="42"/>
       <c r="C92" s="23"/>
       <c r="D92" s="44"/>
       <c r="E92" s="118"/>
       <c r="F92" s="119"/>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="203" t="s">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="223" t="s">
         <v>56</v>
       </c>
-      <c r="B93" s="197"/>
-      <c r="C93" s="197"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="197"/>
-      <c r="B94" s="197"/>
-      <c r="C94" s="197"/>
-    </row>
-    <row r="95" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="220"/>
+      <c r="C93" s="220"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="220"/>
+      <c r="B94" s="220"/>
+      <c r="C94" s="220"/>
+    </row>
+    <row r="95" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="53"/>
       <c r="B95" s="131"/>
       <c r="C95" s="35">
         <v>11948.17</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="53"/>
       <c r="B96" s="35"/>
       <c r="C96" s="35"/>
     </row>
-    <row r="97" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="123"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35">
         <v>61209</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="45" t="s">
         <v>34</v>
       </c>
@@ -3362,39 +3371,44 @@
       </c>
       <c r="C98" s="46"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M99" s="7"/>
     </row>
-    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="202"/>
-      <c r="B100" s="197"/>
-      <c r="C100" s="197"/>
-      <c r="D100" s="197"/>
-      <c r="E100" s="197"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="197"/>
-      <c r="B101" s="197"/>
-      <c r="C101" s="197"/>
-      <c r="D101" s="197"/>
-      <c r="E101" s="197"/>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A102" s="197"/>
-      <c r="B102" s="197"/>
-      <c r="C102" s="197"/>
-      <c r="D102" s="197"/>
-      <c r="E102" s="197"/>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A103" s="197"/>
-      <c r="B103" s="197"/>
-      <c r="C103" s="197"/>
-      <c r="D103" s="197"/>
-      <c r="E103" s="197"/>
+    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="219"/>
+      <c r="B100" s="220"/>
+      <c r="C100" s="220"/>
+      <c r="D100" s="220"/>
+      <c r="E100" s="220"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A101" s="220"/>
+      <c r="B101" s="220"/>
+      <c r="C101" s="220"/>
+      <c r="D101" s="220"/>
+      <c r="E101" s="220"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A102" s="220"/>
+      <c r="B102" s="220"/>
+      <c r="C102" s="220"/>
+      <c r="D102" s="220"/>
+      <c r="E102" s="220"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A103" s="220"/>
+      <c r="B103" s="220"/>
+      <c r="C103" s="220"/>
+      <c r="D103" s="220"/>
+      <c r="E103" s="220"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="A100:E103"/>
     <mergeCell ref="I54:J54"/>
     <mergeCell ref="A35:B35"/>
@@ -3405,11 +3419,6 @@
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="A49:B49"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A30:B30"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3420,163 +3429,163 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T108"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" hidden="1" customWidth="1"/>
-    <col min="2" max="3" width="4.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.42578125" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" customWidth="1"/>
-    <col min="10" max="11" width="9.5703125" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="11.7109375" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" customWidth="1"/>
-    <col min="18" max="18" width="10.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="4.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+    <col min="5" max="5" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.44140625" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" customWidth="1"/>
+    <col min="9" max="9" width="10.5546875" customWidth="1"/>
+    <col min="10" max="11" width="9.5546875" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="11.6640625" customWidth="1"/>
+    <col min="16" max="16" width="14.6640625" customWidth="1"/>
+    <col min="17" max="17" width="14.33203125" customWidth="1"/>
+    <col min="18" max="18" width="10.44140625" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
-      <c r="B1" s="254"/>
-      <c r="C1" s="255"/>
-      <c r="D1" s="256"/>
-      <c r="E1" s="232" t="s">
-        <v>274</v>
-      </c>
-      <c r="F1" s="233">
-        <v>0</v>
-      </c>
-      <c r="G1" s="234"/>
-      <c r="H1" s="245"/>
-      <c r="I1" s="246"/>
-      <c r="J1" s="247"/>
-      <c r="K1" s="236" t="s">
+      <c r="B1" s="246"/>
+      <c r="C1" s="247"/>
+      <c r="D1" s="248"/>
+      <c r="E1" s="198" t="s">
+        <v>272</v>
+      </c>
+      <c r="F1" s="262">
+        <v>0</v>
+      </c>
+      <c r="G1" s="260"/>
+      <c r="H1" s="237"/>
+      <c r="I1" s="238"/>
+      <c r="J1" s="239"/>
+      <c r="K1" s="200" t="s">
         <v>57</v>
       </c>
-      <c r="L1" s="235"/>
-      <c r="M1" s="237">
+      <c r="L1" s="199"/>
+      <c r="M1" s="259">
         <v>4678831.9400000004</v>
       </c>
-      <c r="N1" s="234"/>
-      <c r="O1" s="248">
+      <c r="N1" s="260"/>
+      <c r="O1" s="240">
         <v>3600000</v>
       </c>
-      <c r="P1" s="249"/>
-      <c r="Q1" s="250"/>
+      <c r="P1" s="241"/>
+      <c r="Q1" s="242"/>
       <c r="R1" s="19"/>
     </row>
-    <row r="2" spans="1:20" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6"/>
-      <c r="B2" s="238"/>
-      <c r="C2" s="257"/>
-      <c r="D2" s="258"/>
-      <c r="E2" s="239" t="s">
+      <c r="B2" s="201"/>
+      <c r="C2" s="205"/>
+      <c r="D2" s="206"/>
+      <c r="E2" s="202" t="s">
         <v>58</v>
       </c>
-      <c r="F2" s="240">
+      <c r="F2" s="250">
         <v>1794800.31</v>
       </c>
-      <c r="G2" s="241"/>
-      <c r="H2" s="242" t="s">
-        <v>275</v>
-      </c>
-      <c r="I2" s="243">
+      <c r="G2" s="251"/>
+      <c r="H2" s="203" t="s">
+        <v>273</v>
+      </c>
+      <c r="I2" s="261">
         <v>2000000</v>
       </c>
-      <c r="J2" s="241"/>
-      <c r="K2" s="244" t="s">
+      <c r="J2" s="251"/>
+      <c r="K2" s="204" t="s">
         <v>59</v>
       </c>
-      <c r="L2" s="244"/>
-      <c r="M2" s="243"/>
-      <c r="N2" s="241"/>
-      <c r="O2" s="251">
+      <c r="L2" s="204"/>
+      <c r="M2" s="261"/>
+      <c r="N2" s="251"/>
+      <c r="O2" s="243">
         <v>48523.32</v>
       </c>
-      <c r="P2" s="252"/>
-      <c r="Q2" s="253"/>
-    </row>
-    <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="211" t="s">
+      <c r="P2" s="244"/>
+      <c r="Q2" s="245"/>
+    </row>
+    <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="263" t="s">
         <v>60</v>
       </c>
       <c r="B3" s="114"/>
-      <c r="C3" s="223" t="s">
+      <c r="C3" s="252" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="223" t="s">
+      <c r="D3" s="252" t="s">
         <v>62</v>
       </c>
-      <c r="E3" s="224" t="s">
+      <c r="E3" s="257" t="s">
         <v>63</v>
       </c>
-      <c r="F3" s="225" t="s">
+      <c r="F3" s="269" t="s">
         <v>64</v>
       </c>
-      <c r="G3" s="226" t="s">
+      <c r="G3" s="265" t="s">
         <v>65</v>
       </c>
-      <c r="H3" s="223" t="s">
+      <c r="H3" s="252" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="227" t="s">
+      <c r="I3" s="267" t="s">
         <v>66</v>
       </c>
-      <c r="J3" s="228" t="s">
+      <c r="J3" s="254" t="s">
         <v>67</v>
       </c>
-      <c r="K3" s="229" t="str">
+      <c r="K3" s="256" t="str">
         <f>K2</f>
         <v>Plan de pago metrogas:</v>
       </c>
-      <c r="L3" s="228" t="s">
+      <c r="L3" s="254" t="s">
         <v>68</v>
       </c>
-      <c r="M3" s="228" t="s">
+      <c r="M3" s="254" t="s">
         <v>69</v>
       </c>
-      <c r="N3" s="228" t="s">
+      <c r="N3" s="254" t="s">
         <v>70</v>
       </c>
-      <c r="O3" s="228" t="s">
+      <c r="O3" s="254" t="s">
         <v>71</v>
       </c>
-      <c r="P3" s="230" t="s">
+      <c r="P3" s="197" t="s">
         <v>72</v>
       </c>
-      <c r="Q3" s="231" t="s">
+      <c r="Q3" s="268" t="s">
         <v>73</v>
       </c>
       <c r="T3" s="44"/>
     </row>
-    <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="212"/>
+    <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="264"/>
       <c r="B4" s="114"/>
-      <c r="C4" s="215"/>
-      <c r="D4" s="215"/>
-      <c r="E4" s="214"/>
-      <c r="F4" s="216"/>
-      <c r="G4" s="213"/>
-      <c r="H4" s="215"/>
-      <c r="I4" s="214"/>
-      <c r="J4" s="214"/>
-      <c r="K4" s="215"/>
-      <c r="L4" s="214"/>
-      <c r="M4" s="214"/>
-      <c r="N4" s="214"/>
-      <c r="O4" s="214"/>
+      <c r="C4" s="253"/>
+      <c r="D4" s="253"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="270"/>
+      <c r="G4" s="266"/>
+      <c r="H4" s="253"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="253"/>
+      <c r="L4" s="255"/>
+      <c r="M4" s="255"/>
+      <c r="N4" s="255"/>
+      <c r="O4" s="255"/>
       <c r="P4" s="58" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 15/10</v>
       </c>
-      <c r="Q4" s="215"/>
-    </row>
-    <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q4" s="253"/>
+    </row>
+    <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="60"/>
       <c r="B5" s="60" t="s">
         <v>74</v>
@@ -3639,7 +3648,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="60"/>
       <c r="B6" s="60" t="s">
         <v>76</v>
@@ -3703,7 +3712,7 @@
       </c>
       <c r="S6" s="44"/>
     </row>
-    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="60">
         <v>1</v>
       </c>
@@ -3717,7 +3726,7 @@
         <v>79</v>
       </c>
       <c r="E7" s="73"/>
-      <c r="F7" s="172">
+      <c r="F7" s="171">
         <v>1.4200000000000001E-2</v>
       </c>
       <c r="G7" s="115">
@@ -3767,7 +3776,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="60">
         <v>2</v>
       </c>
@@ -3781,7 +3790,7 @@
         <v>81</v>
       </c>
       <c r="E8" s="73"/>
-      <c r="F8" s="172">
+      <c r="F8" s="171">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G8" s="68">
@@ -3833,7 +3842,7 @@
       </c>
       <c r="T8" s="44"/>
     </row>
-    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="60">
         <v>3</v>
       </c>
@@ -3849,7 +3858,7 @@
       <c r="E9" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="172">
+      <c r="F9" s="171">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G9" s="68">
@@ -3901,7 +3910,7 @@
       </c>
       <c r="T9" s="44"/>
     </row>
-    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="60">
         <v>4</v>
       </c>
@@ -3917,7 +3926,7 @@
       <c r="E10" s="59" t="s">
         <v>87</v>
       </c>
-      <c r="F10" s="172">
+      <c r="F10" s="171">
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G10" s="68">
@@ -3968,7 +3977,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="60">
         <v>5</v>
       </c>
@@ -3982,7 +3991,7 @@
         <v>89</v>
       </c>
       <c r="E11" s="59"/>
-      <c r="F11" s="172">
+      <c r="F11" s="171">
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G11" s="68">
@@ -4033,7 +4042,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="60">
         <v>6</v>
       </c>
@@ -4047,7 +4056,7 @@
         <v>91</v>
       </c>
       <c r="E12" s="73"/>
-      <c r="F12" s="172">
+      <c r="F12" s="171">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G12" s="68">
@@ -4098,62 +4107,62 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="60">
         <v>7</v>
       </c>
-      <c r="B13" s="259" t="s">
+      <c r="B13" s="207" t="s">
         <v>92</v>
       </c>
-      <c r="C13" s="259">
+      <c r="C13" s="207">
         <v>41</v>
       </c>
-      <c r="D13" s="259" t="s">
+      <c r="D13" s="207" t="s">
         <v>93</v>
       </c>
-      <c r="E13" s="260" t="s">
+      <c r="E13" s="208" t="s">
         <v>94</v>
       </c>
-      <c r="F13" s="261">
+      <c r="F13" s="209">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="G13" s="262">
+      <c r="G13" s="210">
         <v>231644.41</v>
       </c>
-      <c r="H13" s="263"/>
-      <c r="I13" s="264">
+      <c r="H13" s="211"/>
+      <c r="I13" s="212">
         <f t="shared" si="0"/>
         <v>231644.41</v>
       </c>
-      <c r="J13" s="264">
+      <c r="J13" s="212">
         <f t="shared" si="1"/>
         <v>6949.3323</v>
       </c>
-      <c r="K13" s="265">
+      <c r="K13" s="213">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L13" s="265">
+      <c r="L13" s="213">
         <f t="shared" si="3"/>
         <v>94512.405188000004</v>
       </c>
-      <c r="M13" s="266">
+      <c r="M13" s="214">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N13" s="266">
+      <c r="N13" s="214">
         <f t="shared" si="5"/>
         <v>36254.966262000002</v>
       </c>
-      <c r="O13" s="266">
+      <c r="O13" s="214">
         <f t="shared" si="6"/>
         <v>40400</v>
       </c>
-      <c r="P13" s="267">
+      <c r="P13" s="215">
         <f t="shared" si="7"/>
         <v>409761.41</v>
       </c>
-      <c r="Q13" s="268">
+      <c r="Q13" s="216">
         <f t="shared" si="8"/>
         <v>422054.41</v>
       </c>
@@ -4162,7 +4171,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="60">
         <v>8</v>
       </c>
@@ -4185,7 +4194,7 @@
         <v>107832.42</v>
       </c>
       <c r="H14" s="115">
-        <f>G14</f>
+        <f t="shared" ref="H14:H19" si="10">G14</f>
         <v>107832.42</v>
       </c>
       <c r="I14" s="69">
@@ -4229,65 +4238,65 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="60">
         <v>1</v>
       </c>
-      <c r="B15" s="173" t="s">
+      <c r="B15" s="172" t="s">
         <v>98</v>
       </c>
-      <c r="C15" s="173">
+      <c r="C15" s="172">
         <v>43</v>
       </c>
-      <c r="D15" s="173" t="s">
+      <c r="D15" s="172" t="s">
         <v>96</v>
       </c>
-      <c r="E15" s="173" t="s">
+      <c r="E15" s="172" t="s">
         <v>99</v>
       </c>
-      <c r="F15" s="174">
+      <c r="F15" s="173">
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="G15" s="175">
+      <c r="G15" s="174">
         <v>107832.43</v>
       </c>
-      <c r="H15" s="186">
-        <f>G15</f>
+      <c r="H15" s="185">
+        <f t="shared" si="10"/>
         <v>107832.43</v>
       </c>
-      <c r="I15" s="176">
+      <c r="I15" s="175">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="176">
+      <c r="J15" s="175">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K15" s="177">
+      <c r="K15" s="176">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L15" s="177">
+      <c r="L15" s="176">
         <f t="shared" si="3"/>
         <v>65035.763965999999</v>
       </c>
-      <c r="M15" s="178">
+      <c r="M15" s="177">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N15" s="178">
+      <c r="N15" s="177">
         <f t="shared" si="5"/>
         <v>24947.724309000001</v>
       </c>
-      <c r="O15" s="178">
+      <c r="O15" s="177">
         <f t="shared" si="6"/>
         <v>27800</v>
       </c>
-      <c r="P15" s="179">
+      <c r="P15" s="178">
         <f t="shared" si="7"/>
         <v>117783.43</v>
       </c>
-      <c r="Q15" s="180">
+      <c r="Q15" s="179">
         <f t="shared" si="8"/>
         <v>121317.43</v>
       </c>
@@ -4296,7 +4305,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="60">
         <v>1</v>
       </c>
@@ -4312,14 +4321,14 @@
       <c r="E16" s="73" t="s">
         <v>102</v>
       </c>
-      <c r="F16" s="172">
+      <c r="F16" s="171">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G16" s="163">
         <v>156705.44</v>
       </c>
       <c r="H16" s="115">
-        <f>G16</f>
+        <f t="shared" si="10"/>
         <v>156705.44</v>
       </c>
       <c r="I16" s="69">
@@ -4363,7 +4372,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="60">
         <v>2</v>
       </c>
@@ -4386,7 +4395,7 @@
         <v>156705.45000000001</v>
       </c>
       <c r="H17" s="115">
-        <f>G17</f>
+        <f t="shared" si="10"/>
         <v>156705.45000000001</v>
       </c>
       <c r="I17" s="69">
@@ -4430,7 +4439,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="60">
         <v>2</v>
       </c>
@@ -4453,7 +4462,7 @@
         <v>107832.46</v>
       </c>
       <c r="H18" s="115">
-        <f>G18</f>
+        <f t="shared" si="10"/>
         <v>107832.46</v>
       </c>
       <c r="I18" s="69">
@@ -4498,7 +4507,7 @@
       </c>
       <c r="S18" s="116"/>
     </row>
-    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="60">
         <v>3</v>
       </c>
@@ -4521,7 +4530,7 @@
         <v>107832.47</v>
       </c>
       <c r="H19" s="115">
-        <f>G19</f>
+        <f t="shared" si="10"/>
         <v>107832.47</v>
       </c>
       <c r="I19" s="69">
@@ -4566,7 +4575,7 @@
       </c>
       <c r="S19" s="116"/>
     </row>
-    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="60">
         <v>3</v>
       </c>
@@ -4582,7 +4591,7 @@
       <c r="E20" s="59" t="s">
         <v>110</v>
       </c>
-      <c r="F20" s="172">
+      <c r="F20" s="171">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G20" s="163">
@@ -4635,7 +4644,7 @@
       <c r="S20" s="116"/>
       <c r="T20" s="43"/>
     </row>
-    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="60">
         <v>4</v>
       </c>
@@ -4651,7 +4660,7 @@
       <c r="E21" s="73" t="s">
         <v>112</v>
       </c>
-      <c r="F21" s="172">
+      <c r="F21" s="171">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G21" s="163">
@@ -4702,62 +4711,62 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="60">
         <v>4</v>
       </c>
-      <c r="B22" s="173" t="s">
+      <c r="B22" s="172" t="s">
         <v>113</v>
       </c>
-      <c r="C22" s="173">
+      <c r="C22" s="172">
         <v>50</v>
       </c>
-      <c r="D22" s="173" t="s">
+      <c r="D22" s="172" t="s">
         <v>96</v>
       </c>
-      <c r="E22" s="222"/>
-      <c r="F22" s="174">
+      <c r="E22" s="196"/>
+      <c r="F22" s="173">
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="G22" s="175">
+      <c r="G22" s="174">
         <v>498093.5</v>
       </c>
-      <c r="H22" s="186">
+      <c r="H22" s="185">
         <v>150000</v>
       </c>
-      <c r="I22" s="176">
+      <c r="I22" s="175">
         <f t="shared" si="0"/>
         <v>348093.5</v>
       </c>
-      <c r="J22" s="176">
+      <c r="J22" s="175">
         <f t="shared" si="1"/>
         <v>10442.805</v>
       </c>
-      <c r="K22" s="177">
+      <c r="K22" s="176">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L22" s="177">
+      <c r="L22" s="176">
         <f t="shared" si="3"/>
         <v>65035.763965999999</v>
       </c>
-      <c r="M22" s="178">
+      <c r="M22" s="177">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N22" s="178">
+      <c r="N22" s="177">
         <f t="shared" si="5"/>
         <v>24947.724309000001</v>
       </c>
-      <c r="O22" s="178">
+      <c r="O22" s="177">
         <f t="shared" si="6"/>
         <v>27800</v>
       </c>
-      <c r="P22" s="179">
+      <c r="P22" s="178">
         <f t="shared" si="7"/>
         <v>476320.5</v>
       </c>
-      <c r="Q22" s="180">
+      <c r="Q22" s="179">
         <f t="shared" si="8"/>
         <v>490610.5</v>
       </c>
@@ -4766,7 +4775,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="60">
         <v>5</v>
       </c>
@@ -4830,7 +4839,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="60">
         <v>5</v>
       </c>
@@ -4897,8 +4906,8 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="173">
+    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="172">
         <v>6</v>
       </c>
       <c r="B25" s="59" t="s">
@@ -4911,7 +4920,7 @@
         <v>120</v>
       </c>
       <c r="E25" s="73"/>
-      <c r="F25" s="172">
+      <c r="F25" s="171">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G25" s="163">
@@ -4928,31 +4937,31 @@
         <f t="shared" si="1"/>
         <v>705.63149999999962</v>
       </c>
-      <c r="K25" s="218">
+      <c r="K25" s="192">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L25" s="218">
+      <c r="L25" s="192">
         <f t="shared" si="3"/>
         <v>94512.405188000004</v>
       </c>
-      <c r="M25" s="219">
+      <c r="M25" s="193">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N25" s="219">
+      <c r="N25" s="193">
         <f t="shared" si="5"/>
         <v>36254.966262000002</v>
       </c>
-      <c r="O25" s="219">
+      <c r="O25" s="193">
         <f t="shared" si="6"/>
         <v>40400</v>
       </c>
-      <c r="P25" s="220">
+      <c r="P25" s="194">
         <f t="shared" si="7"/>
         <v>195394.53</v>
       </c>
-      <c r="Q25" s="221">
+      <c r="Q25" s="195">
         <f t="shared" si="8"/>
         <v>201256.53</v>
       </c>
@@ -4961,7 +4970,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="60">
         <v>6</v>
       </c>
@@ -5028,7 +5037,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="60">
         <v>7</v>
       </c>
@@ -5044,7 +5053,7 @@
       <c r="E27" s="73" t="s">
         <v>125</v>
       </c>
-      <c r="F27" s="172">
+      <c r="F27" s="171">
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G27" s="68">
@@ -5092,7 +5101,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="60">
         <v>7</v>
       </c>
@@ -5108,7 +5117,7 @@
       <c r="E28" s="73" t="s">
         <v>128</v>
       </c>
-      <c r="F28" s="172">
+      <c r="F28" s="171">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G28" s="163">
@@ -5126,31 +5135,31 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K28" s="218">
+      <c r="K28" s="192">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L28" s="218">
+      <c r="L28" s="192">
         <f t="shared" si="3"/>
         <v>94512.405188000004</v>
       </c>
-      <c r="M28" s="219">
+      <c r="M28" s="193">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N28" s="219">
+      <c r="N28" s="193">
         <f t="shared" si="5"/>
         <v>36254.966262000002</v>
       </c>
-      <c r="O28" s="219">
+      <c r="O28" s="193">
         <f t="shared" si="6"/>
         <v>40400</v>
       </c>
-      <c r="P28" s="220">
+      <c r="P28" s="194">
         <f t="shared" si="7"/>
         <v>166376.56</v>
       </c>
-      <c r="Q28" s="221">
+      <c r="Q28" s="195">
         <f t="shared" si="8"/>
         <v>171367.56</v>
       </c>
@@ -5159,7 +5168,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="60">
         <v>8</v>
       </c>
@@ -5224,7 +5233,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="60">
         <v>8</v>
       </c>
@@ -5288,7 +5297,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="60">
         <v>9</v>
       </c>
@@ -5353,7 +5362,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="60">
         <v>9</v>
       </c>
@@ -5367,7 +5376,7 @@
         <v>137</v>
       </c>
       <c r="E32" s="59"/>
-      <c r="F32" s="172">
+      <c r="F32" s="171">
         <v>2.0199999999999999E-2</v>
       </c>
       <c r="G32" s="68">
@@ -5418,60 +5427,60 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="173">
+    <row r="33" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="172">
         <v>10</v>
       </c>
-      <c r="B33" s="173" t="s">
+      <c r="B33" s="172" t="s">
         <v>138</v>
       </c>
-      <c r="C33" s="173">
+      <c r="C33" s="172">
         <v>61</v>
       </c>
-      <c r="D33" s="173" t="s">
+      <c r="D33" s="172" t="s">
         <v>139</v>
       </c>
-      <c r="E33" s="173"/>
-      <c r="F33" s="174">
+      <c r="E33" s="172"/>
+      <c r="F33" s="173">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="G33" s="175">
+      <c r="G33" s="174">
         <v>156705.60999999999</v>
       </c>
-      <c r="H33" s="186"/>
-      <c r="I33" s="176">
+      <c r="H33" s="185"/>
+      <c r="I33" s="175">
         <f t="shared" si="0"/>
         <v>156705.60999999999</v>
       </c>
-      <c r="J33" s="176">
+      <c r="J33" s="175">
         <f t="shared" si="1"/>
         <v>4701.1682999999994</v>
       </c>
-      <c r="K33" s="177">
+      <c r="K33" s="176">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L33" s="177">
+      <c r="L33" s="176">
         <f t="shared" si="3"/>
         <v>94512.405188000004</v>
       </c>
-      <c r="M33" s="178">
+      <c r="M33" s="177">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N33" s="178">
+      <c r="N33" s="177">
         <f t="shared" si="5"/>
         <v>36254.966262000002</v>
       </c>
-      <c r="O33" s="178">
+      <c r="O33" s="177">
         <f t="shared" si="6"/>
         <v>40400</v>
       </c>
-      <c r="P33" s="179">
+      <c r="P33" s="178">
         <f t="shared" si="7"/>
         <v>332574.61</v>
       </c>
-      <c r="Q33" s="180">
+      <c r="Q33" s="179">
         <f t="shared" si="8"/>
         <v>342551.61</v>
       </c>
@@ -5480,7 +5489,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="60">
         <v>10</v>
       </c>
@@ -5496,7 +5505,7 @@
       <c r="E34" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="F34" s="172">
+      <c r="F34" s="171">
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="G34" s="68">
@@ -5547,7 +5556,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" s="60">
         <v>11</v>
       </c>
@@ -5614,7 +5623,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="60">
         <v>11</v>
       </c>
@@ -5681,7 +5690,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="60">
         <v>12</v>
       </c>
@@ -5708,47 +5717,47 @@
         <v>156705.65</v>
       </c>
       <c r="I37" s="69">
-        <f t="shared" ref="I37:I56" si="10">G37-H37</f>
+        <f t="shared" ref="I37:I56" si="11">G37-H37</f>
         <v>0</v>
       </c>
       <c r="J37" s="69">
-        <f t="shared" ref="J37:J56" si="11">IF(I37&gt;0,I37*3%,0)</f>
+        <f t="shared" ref="J37:J56" si="12">IF(I37&gt;0,I37*3%,0)</f>
         <v>0</v>
       </c>
       <c r="K37" s="70">
-        <f t="shared" ref="K37:K56" si="12">M$2*F37</f>
+        <f t="shared" ref="K37:K56" si="13">M$2*F37</f>
         <v>0</v>
       </c>
       <c r="L37" s="70">
-        <f t="shared" ref="L37:L68" si="13">M$1*F37</f>
+        <f t="shared" ref="L37:L68" si="14">M$1*F37</f>
         <v>94512.405188000004</v>
       </c>
       <c r="M37" s="122">
-        <f t="shared" ref="M37:M56" si="14">F$1*F37</f>
+        <f t="shared" ref="M37:M56" si="15">F$1*F37</f>
         <v>0</v>
       </c>
       <c r="N37" s="122">
-        <f t="shared" ref="N37:N56" si="15">F$2*F37</f>
+        <f t="shared" ref="N37:N56" si="16">F$2*F37</f>
         <v>36254.966262000002</v>
       </c>
       <c r="O37" s="122">
-        <f t="shared" ref="O37:O68" si="16">I$2*F37</f>
+        <f t="shared" ref="O37:O68" si="17">I$2*F37</f>
         <v>40400</v>
       </c>
       <c r="P37" s="71">
-        <f t="shared" ref="P37:P68" si="17">ROUND(SUM(I37:O37),0) + R37</f>
+        <f t="shared" ref="P37:P68" si="18">ROUND(SUM(I37:O37),0) + R37</f>
         <v>171167.65</v>
       </c>
       <c r="Q37" s="72">
-        <f t="shared" ref="Q37:Q56" si="18">ROUND(P37*3%,0) + P37</f>
+        <f t="shared" ref="Q37:Q56" si="19">ROUND(P37*3%,0) + P37</f>
         <v>176302.65</v>
       </c>
       <c r="R37" s="44">
-        <f t="shared" ref="R37:R68" si="19">ROUND(0.001+C37/100,2)</f>
+        <f t="shared" ref="R37:R68" si="20">ROUND(0.001+C37/100,2)</f>
         <v>0.65</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="60">
         <v>12</v>
       </c>
@@ -5772,47 +5781,47 @@
       </c>
       <c r="H38" s="115"/>
       <c r="I38" s="69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>219614.66</v>
       </c>
       <c r="J38" s="69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6588.4398000000001</v>
       </c>
       <c r="K38" s="70">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L38" s="70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>65035.763965999999</v>
       </c>
       <c r="M38" s="122">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N38" s="122">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>24947.724309000001</v>
       </c>
       <c r="O38" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>27800</v>
       </c>
       <c r="P38" s="71">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>343987.66</v>
       </c>
       <c r="Q38" s="72">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>354307.66</v>
       </c>
       <c r="R38" s="44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.66</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="60">
         <v>1</v>
       </c>
@@ -5839,47 +5848,47 @@
         <v>201142.66999999998</v>
       </c>
       <c r="I39" s="69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J39" s="69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K39" s="70">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L39" s="70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>65035.763965999999</v>
       </c>
       <c r="M39" s="122">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N39" s="122">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>24947.724309000001</v>
       </c>
       <c r="O39" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>27800</v>
       </c>
       <c r="P39" s="71">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>117783.67</v>
       </c>
       <c r="Q39" s="72">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>121317.67</v>
       </c>
       <c r="R39" s="44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.67</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="60">
         <v>1</v>
       </c>
@@ -5904,47 +5913,47 @@
       </c>
       <c r="H40" s="115"/>
       <c r="I40" s="69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>156705.68</v>
       </c>
       <c r="J40" s="69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4701.1704</v>
       </c>
       <c r="K40" s="70">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L40" s="70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>94512.405188000004</v>
       </c>
       <c r="M40" s="122">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N40" s="122">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>36254.966262000002</v>
       </c>
       <c r="O40" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>40400</v>
       </c>
       <c r="P40" s="71">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>332574.68</v>
       </c>
       <c r="Q40" s="72">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>342551.68</v>
       </c>
       <c r="R40" s="44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.68</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="59">
         <v>1</v>
       </c>
@@ -5971,47 +5980,47 @@
         <v>156705.69</v>
       </c>
       <c r="I41" s="69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J41" s="69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K41" s="70">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L41" s="70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>94512.405188000004</v>
       </c>
       <c r="M41" s="122">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N41" s="122">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>36254.966262000002</v>
       </c>
       <c r="O41" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>40400</v>
       </c>
       <c r="P41" s="71">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>171167.69</v>
       </c>
       <c r="Q41" s="72">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>176302.69</v>
       </c>
       <c r="R41" s="44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.69</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="60">
         <v>2</v>
       </c>
@@ -6038,47 +6047,47 @@
         <v>206354.7</v>
       </c>
       <c r="I42" s="69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>22706</v>
       </c>
       <c r="J42" s="69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>681.18</v>
       </c>
       <c r="K42" s="70">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L42" s="70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>65035.763965999999</v>
       </c>
       <c r="M42" s="122">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N42" s="122">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>24947.724309000001</v>
       </c>
       <c r="O42" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>27800</v>
       </c>
       <c r="P42" s="71">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>141171.70000000001</v>
       </c>
       <c r="Q42" s="72">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>145406.70000000001</v>
       </c>
       <c r="R42" s="44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="60">
         <v>2</v>
       </c>
@@ -6102,111 +6111,111 @@
       </c>
       <c r="H43" s="115"/>
       <c r="I43" s="69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>107832.71</v>
       </c>
       <c r="J43" s="69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3234.9812999999999</v>
       </c>
       <c r="K43" s="70">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L43" s="70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>65035.763965999999</v>
       </c>
       <c r="M43" s="122">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N43" s="122">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>24947.724309000001</v>
       </c>
       <c r="O43" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>27800</v>
       </c>
       <c r="P43" s="71">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>228851.71</v>
       </c>
       <c r="Q43" s="72">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>235717.71</v>
       </c>
       <c r="R43" s="44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.71</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="60">
         <v>2</v>
       </c>
-      <c r="B44" s="269" t="s">
+      <c r="B44" s="217" t="s">
         <v>168</v>
       </c>
-      <c r="C44" s="259">
+      <c r="C44" s="207">
         <v>72</v>
       </c>
-      <c r="D44" s="259" t="s">
+      <c r="D44" s="207" t="s">
         <v>166</v>
       </c>
-      <c r="E44" s="259" t="s">
+      <c r="E44" s="207" t="s">
         <v>246</v>
       </c>
-      <c r="F44" s="270">
+      <c r="F44" s="218">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="G44" s="262">
+      <c r="G44" s="210">
         <v>486538.72</v>
       </c>
-      <c r="H44" s="263"/>
-      <c r="I44" s="264">
-        <f t="shared" si="10"/>
+      <c r="H44" s="211"/>
+      <c r="I44" s="212">
+        <f t="shared" si="11"/>
         <v>486538.72</v>
       </c>
-      <c r="J44" s="264">
-        <f t="shared" si="11"/>
+      <c r="J44" s="212">
+        <f t="shared" si="12"/>
         <v>14596.161599999999</v>
       </c>
-      <c r="K44" s="265">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L44" s="265">
+      <c r="K44" s="213">
         <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L44" s="213">
+        <f t="shared" si="14"/>
         <v>94512.405188000004</v>
       </c>
-      <c r="M44" s="266">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N44" s="266">
+      <c r="M44" s="214">
         <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N44" s="214">
+        <f t="shared" si="16"/>
         <v>36254.966262000002</v>
       </c>
-      <c r="O44" s="266">
-        <f t="shared" si="16"/>
+      <c r="O44" s="214">
+        <f t="shared" si="17"/>
         <v>40400</v>
       </c>
-      <c r="P44" s="267">
-        <f t="shared" si="17"/>
+      <c r="P44" s="215">
+        <f t="shared" si="18"/>
         <v>672302.72</v>
       </c>
-      <c r="Q44" s="268">
-        <f t="shared" si="18"/>
+      <c r="Q44" s="216">
+        <f t="shared" si="19"/>
         <v>692471.72</v>
       </c>
       <c r="R44" s="44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.72</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="60">
         <v>3</v>
       </c>
@@ -6232,47 +6241,47 @@
         <v>200000.73</v>
       </c>
       <c r="I45" s="69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>489174</v>
       </c>
       <c r="J45" s="69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>14675.22</v>
       </c>
       <c r="K45" s="70">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L45" s="70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>94512.405188000004</v>
       </c>
       <c r="M45" s="122">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N45" s="122">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>36254.966262000002</v>
       </c>
       <c r="O45" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>40400</v>
       </c>
       <c r="P45" s="71">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>675017.73</v>
       </c>
       <c r="Q45" s="72">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>695268.73</v>
       </c>
       <c r="R45" s="44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.73</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="60">
         <v>3</v>
       </c>
@@ -6299,47 +6308,47 @@
         <v>107832.74</v>
       </c>
       <c r="I46" s="69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J46" s="69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K46" s="70">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L46" s="70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>65035.763965999999</v>
       </c>
       <c r="M46" s="122">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N46" s="122">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>24947.724309000001</v>
       </c>
       <c r="O46" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>27800</v>
       </c>
       <c r="P46" s="71">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>117783.74</v>
       </c>
       <c r="Q46" s="72">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>121317.74</v>
       </c>
       <c r="R46" s="44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.74</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="60">
         <v>3</v>
       </c>
@@ -6363,48 +6372,48 @@
       </c>
       <c r="H47" s="115"/>
       <c r="I47" s="69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>107832.75</v>
       </c>
       <c r="J47" s="69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3234.9825000000001</v>
       </c>
       <c r="K47" s="70">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L47" s="70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>65035.763965999999</v>
       </c>
       <c r="M47" s="122">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N47" s="122">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>24947.724309000001</v>
       </c>
       <c r="O47" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>27800</v>
       </c>
       <c r="P47" s="71">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>228851.75</v>
       </c>
       <c r="Q47" s="72">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>235717.75</v>
       </c>
       <c r="R47" s="44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.75</v>
       </c>
       <c r="T47" s="136"/>
     </row>
-    <row r="48" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="60">
         <v>4</v>
       </c>
@@ -6431,47 +6440,47 @@
         <v>156705.76</v>
       </c>
       <c r="I48" s="69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J48" s="69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K48" s="70">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L48" s="70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>94512.405188000004</v>
       </c>
       <c r="M48" s="122">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N48" s="122">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>36254.966262000002</v>
       </c>
       <c r="O48" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>40400</v>
       </c>
       <c r="P48" s="71">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>171167.76</v>
       </c>
       <c r="Q48" s="72">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>176302.76</v>
       </c>
       <c r="R48" s="44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.76</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="60">
         <v>4</v>
       </c>
@@ -6498,47 +6507,47 @@
         <v>156705.76999999999</v>
       </c>
       <c r="I49" s="69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J49" s="69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K49" s="70">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L49" s="70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>94512.405188000004</v>
       </c>
       <c r="M49" s="122">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N49" s="122">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>36254.966262000002</v>
       </c>
       <c r="O49" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>40400</v>
       </c>
       <c r="P49" s="71">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>171167.77</v>
       </c>
       <c r="Q49" s="72">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>176302.77</v>
       </c>
       <c r="R49" s="44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.77</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="60">
         <v>4</v>
       </c>
@@ -6565,109 +6574,112 @@
         <v>196760.68</v>
       </c>
       <c r="I50" s="69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J50" s="69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K50" s="70">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L50" s="70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>65035.763965999999</v>
       </c>
       <c r="M50" s="122">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N50" s="122">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>24947.724309000001</v>
       </c>
       <c r="O50" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>27800</v>
       </c>
       <c r="P50" s="71">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>117783.78</v>
       </c>
       <c r="Q50" s="72">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>121317.78</v>
       </c>
       <c r="R50" s="44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.78</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="60">
         <v>5</v>
       </c>
-      <c r="B51" s="75" t="s">
+      <c r="B51" s="271" t="s">
         <v>185</v>
       </c>
-      <c r="C51" s="60">
+      <c r="C51" s="272">
         <v>79</v>
       </c>
-      <c r="D51" s="59" t="s">
+      <c r="D51" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="E51" s="73"/>
-      <c r="F51" s="74">
+      <c r="E51" s="273"/>
+      <c r="F51" s="274">
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="G51" s="68">
+      <c r="G51" s="275">
         <v>111067.69</v>
       </c>
-      <c r="H51" s="115"/>
-      <c r="I51" s="69">
-        <f t="shared" si="10"/>
+      <c r="H51" s="276"/>
+      <c r="I51" s="277">
+        <f t="shared" si="11"/>
         <v>111067.69</v>
       </c>
-      <c r="J51" s="69">
-        <f t="shared" si="11"/>
+      <c r="J51" s="277">
+        <f t="shared" si="12"/>
         <v>3332.0306999999998</v>
       </c>
-      <c r="K51" s="70">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L51" s="70">
+      <c r="K51" s="278">
         <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L51" s="278">
+        <f t="shared" si="14"/>
         <v>65035.763965999999</v>
       </c>
-      <c r="M51" s="122">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N51" s="122">
+      <c r="M51" s="279">
         <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N51" s="279">
+        <f t="shared" si="16"/>
         <v>24947.724309000001</v>
       </c>
-      <c r="O51" s="122">
-        <f t="shared" si="16"/>
+      <c r="O51" s="279">
+        <f t="shared" si="17"/>
         <v>27800</v>
       </c>
-      <c r="P51" s="71">
-        <f t="shared" si="17"/>
+      <c r="P51" s="280">
+        <f t="shared" si="18"/>
         <v>232183.79</v>
       </c>
-      <c r="Q51" s="72">
-        <f t="shared" si="18"/>
+      <c r="Q51" s="281">
+        <f t="shared" si="19"/>
         <v>239149.79</v>
       </c>
       <c r="R51" s="44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.79</v>
       </c>
-    </row>
-    <row r="52" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S51" s="282" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="60">
         <v>5</v>
       </c>
@@ -6694,47 +6706,47 @@
         <v>153006.79999999999</v>
       </c>
       <c r="I52" s="69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J52" s="69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K52" s="70">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L52" s="70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>94512.405188000004</v>
       </c>
       <c r="M52" s="122">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N52" s="122">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>36254.966262000002</v>
       </c>
       <c r="O52" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>40400</v>
       </c>
       <c r="P52" s="71">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>171167.8</v>
       </c>
       <c r="Q52" s="72">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>176302.8</v>
       </c>
       <c r="R52" s="44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.8</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="60">
         <v>5</v>
       </c>
@@ -6761,50 +6773,50 @@
         <v>292307.81</v>
       </c>
       <c r="I53" s="69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J53" s="69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K53" s="70">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L53" s="70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>94512.405188000004</v>
       </c>
       <c r="M53" s="122">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N53" s="122">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>36254.966262000002</v>
       </c>
       <c r="O53" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>40400</v>
       </c>
       <c r="P53" s="71">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>171167.81</v>
       </c>
       <c r="Q53" s="72">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>176302.81</v>
       </c>
       <c r="R53" s="44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.81</v>
       </c>
       <c r="T53" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="60">
         <v>6</v>
       </c>
@@ -6829,111 +6841,111 @@
         <v>107832.82</v>
       </c>
       <c r="I54" s="69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J54" s="69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K54" s="70">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L54" s="70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>65035.763965999999</v>
       </c>
       <c r="M54" s="122">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N54" s="122">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>24947.724309000001</v>
       </c>
       <c r="O54" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>27800</v>
       </c>
       <c r="P54" s="71">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>117783.82</v>
       </c>
       <c r="Q54" s="72">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>121317.82</v>
       </c>
       <c r="R54" s="44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.82</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="60">
         <v>6</v>
       </c>
-      <c r="B55" s="269" t="s">
+      <c r="B55" s="217" t="s">
         <v>195</v>
       </c>
-      <c r="C55" s="259">
+      <c r="C55" s="207">
         <v>83</v>
       </c>
-      <c r="D55" s="259" t="s">
+      <c r="D55" s="207" t="s">
         <v>196</v>
       </c>
-      <c r="E55" s="259" t="s">
+      <c r="E55" s="207" t="s">
         <v>197</v>
       </c>
-      <c r="F55" s="270">
+      <c r="F55" s="218">
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="G55" s="262">
+      <c r="G55" s="210">
         <v>545112.82999999996</v>
       </c>
-      <c r="H55" s="263"/>
-      <c r="I55" s="264">
-        <f t="shared" si="10"/>
+      <c r="H55" s="211"/>
+      <c r="I55" s="212">
+        <f t="shared" si="11"/>
         <v>545112.82999999996</v>
       </c>
-      <c r="J55" s="264">
-        <f t="shared" si="11"/>
+      <c r="J55" s="212">
+        <f t="shared" si="12"/>
         <v>16353.384899999997</v>
       </c>
-      <c r="K55" s="265">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L55" s="265">
+      <c r="K55" s="213">
         <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L55" s="213">
+        <f t="shared" si="14"/>
         <v>65035.763965999999</v>
       </c>
-      <c r="M55" s="266">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N55" s="266">
+      <c r="M55" s="214">
         <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="N55" s="214">
+        <f t="shared" si="16"/>
         <v>24947.724309000001</v>
       </c>
-      <c r="O55" s="266">
-        <f t="shared" si="16"/>
+      <c r="O55" s="214">
+        <f t="shared" si="17"/>
         <v>27800</v>
       </c>
-      <c r="P55" s="267">
-        <f t="shared" si="17"/>
+      <c r="P55" s="215">
+        <f t="shared" si="18"/>
         <v>679250.83</v>
       </c>
-      <c r="Q55" s="268">
-        <f t="shared" si="18"/>
+      <c r="Q55" s="216">
+        <f t="shared" si="19"/>
         <v>699628.83</v>
       </c>
       <c r="R55" s="44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.83</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="60">
         <v>6</v>
       </c>
@@ -6955,47 +6967,47 @@
       </c>
       <c r="H56" s="115"/>
       <c r="I56" s="69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>156705.84</v>
       </c>
       <c r="J56" s="69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4701.1751999999997</v>
       </c>
       <c r="K56" s="70">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L56" s="70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>94512.405188000004</v>
       </c>
       <c r="M56" s="122">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="N56" s="122">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>36254.966262000002</v>
       </c>
       <c r="O56" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>40400</v>
       </c>
       <c r="P56" s="71">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>332574.84000000003</v>
       </c>
       <c r="Q56" s="72">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>342551.84</v>
       </c>
       <c r="R56" s="44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.84</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="60">
         <v>7</v>
       </c>
@@ -7012,26 +7024,26 @@
       <c r="J57" s="69"/>
       <c r="K57" s="70"/>
       <c r="L57" s="70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M57" s="122"/>
       <c r="N57" s="122"/>
       <c r="O57" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P57" s="71">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q57" s="72"/>
       <c r="R57" s="44">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="60">
         <v>7</v>
       </c>
@@ -7048,26 +7060,26 @@
       <c r="J58" s="69"/>
       <c r="K58" s="70"/>
       <c r="L58" s="70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M58" s="122"/>
       <c r="N58" s="122"/>
       <c r="O58" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P58" s="71">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q58" s="72"/>
       <c r="R58" s="44">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="60">
         <v>7</v>
       </c>
@@ -7094,109 +7106,109 @@
         <v>46306.17</v>
       </c>
       <c r="I59" s="69">
-        <f t="shared" ref="I59:I90" si="20">G59-H59</f>
+        <f t="shared" ref="I59:I90" si="21">G59-H59</f>
         <v>0</v>
       </c>
       <c r="J59" s="69">
-        <f t="shared" ref="J59:J90" si="21">IF(I59&gt;0,I59*3%,0)</f>
+        <f t="shared" ref="J59:J90" si="22">IF(I59&gt;0,I59*3%,0)</f>
         <v>0</v>
       </c>
       <c r="K59" s="70">
-        <f t="shared" ref="K59:K90" si="22">M$2*F59</f>
+        <f t="shared" ref="K59:K90" si="23">M$2*F59</f>
         <v>0</v>
       </c>
       <c r="L59" s="70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>14972.262208000002</v>
       </c>
       <c r="M59" s="122">
-        <f t="shared" ref="M59:M90" si="23">F$1*F59</f>
+        <f t="shared" ref="M59:M90" si="24">F$1*F59</f>
         <v>0</v>
       </c>
       <c r="N59" s="122">
-        <f t="shared" ref="N59:N90" si="24">F$2*F59</f>
+        <f t="shared" ref="N59:N90" si="25">F$2*F59</f>
         <v>5743.3609920000008</v>
       </c>
       <c r="O59" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>6400</v>
       </c>
       <c r="P59" s="71">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>27116.17</v>
       </c>
       <c r="Q59" s="72">
-        <f t="shared" ref="Q59:Q90" si="25">ROUND(P59*3%,0) + P59</f>
+        <f t="shared" ref="Q59:Q90" si="26">ROUND(P59*3%,0) + P59</f>
         <v>27929.17</v>
       </c>
       <c r="R59" s="44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="60">
         <v>8</v>
       </c>
-      <c r="B60" s="269" t="s">
+      <c r="B60" s="217" t="s">
         <v>202</v>
       </c>
-      <c r="C60" s="259">
+      <c r="C60" s="207">
         <v>18</v>
       </c>
-      <c r="D60" s="259" t="s">
+      <c r="D60" s="207" t="s">
         <v>203</v>
       </c>
-      <c r="E60" s="260"/>
-      <c r="F60" s="270">
+      <c r="E60" s="208"/>
+      <c r="F60" s="218">
         <v>3.3E-3</v>
       </c>
-      <c r="G60" s="262">
+      <c r="G60" s="210">
         <v>261855.18</v>
       </c>
-      <c r="H60" s="263"/>
-      <c r="I60" s="264">
+      <c r="H60" s="211"/>
+      <c r="I60" s="212">
+        <f t="shared" si="21"/>
+        <v>261855.18</v>
+      </c>
+      <c r="J60" s="212">
+        <f t="shared" si="22"/>
+        <v>7855.6553999999996</v>
+      </c>
+      <c r="K60" s="213">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="L60" s="213">
+        <f t="shared" si="14"/>
+        <v>15440.145402000002</v>
+      </c>
+      <c r="M60" s="214">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="214">
+        <f t="shared" si="25"/>
+        <v>5922.841023</v>
+      </c>
+      <c r="O60" s="214">
+        <f t="shared" si="17"/>
+        <v>6600</v>
+      </c>
+      <c r="P60" s="215">
+        <f t="shared" si="18"/>
+        <v>297674.18</v>
+      </c>
+      <c r="Q60" s="216">
+        <f t="shared" si="26"/>
+        <v>306604.18</v>
+      </c>
+      <c r="R60" s="44">
         <f t="shared" si="20"/>
-        <v>261855.18</v>
-      </c>
-      <c r="J60" s="264">
-        <f t="shared" si="21"/>
-        <v>7855.6553999999996</v>
-      </c>
-      <c r="K60" s="265">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L60" s="265">
-        <f t="shared" si="13"/>
-        <v>15440.145402000002</v>
-      </c>
-      <c r="M60" s="266">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N60" s="266">
-        <f t="shared" si="24"/>
-        <v>5922.841023</v>
-      </c>
-      <c r="O60" s="266">
-        <f t="shared" si="16"/>
-        <v>6600</v>
-      </c>
-      <c r="P60" s="267">
-        <f t="shared" si="17"/>
-        <v>297674.18</v>
-      </c>
-      <c r="Q60" s="268">
-        <f t="shared" si="25"/>
-        <v>306604.18</v>
-      </c>
-      <c r="R60" s="44">
-        <f t="shared" si="19"/>
         <v>0.18</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="60">
         <v>8</v>
       </c>
@@ -7218,47 +7230,47 @@
       </c>
       <c r="H61" s="115"/>
       <c r="I61" s="69">
+        <f t="shared" si="21"/>
+        <v>13301.19</v>
+      </c>
+      <c r="J61" s="69">
+        <f t="shared" si="22"/>
+        <v>399.03570000000002</v>
+      </c>
+      <c r="K61" s="70">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="L61" s="70">
+        <f t="shared" si="14"/>
+        <v>1871.5327760000002</v>
+      </c>
+      <c r="M61" s="122">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N61" s="122">
+        <f t="shared" si="25"/>
+        <v>717.9201240000001</v>
+      </c>
+      <c r="O61" s="122">
+        <f t="shared" si="17"/>
+        <v>800</v>
+      </c>
+      <c r="P61" s="71">
+        <f t="shared" si="18"/>
+        <v>17090.189999999999</v>
+      </c>
+      <c r="Q61" s="72">
+        <f t="shared" si="26"/>
+        <v>17603.189999999999</v>
+      </c>
+      <c r="R61" s="44">
         <f t="shared" si="20"/>
-        <v>13301.19</v>
-      </c>
-      <c r="J61" s="69">
-        <f t="shared" si="21"/>
-        <v>399.03570000000002</v>
-      </c>
-      <c r="K61" s="70">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L61" s="70">
-        <f t="shared" si="13"/>
-        <v>1871.5327760000002</v>
-      </c>
-      <c r="M61" s="122">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N61" s="122">
-        <f t="shared" si="24"/>
-        <v>717.9201240000001</v>
-      </c>
-      <c r="O61" s="122">
-        <f t="shared" si="16"/>
-        <v>800</v>
-      </c>
-      <c r="P61" s="71">
-        <f t="shared" si="17"/>
-        <v>17090.189999999999</v>
-      </c>
-      <c r="Q61" s="72">
-        <f t="shared" si="25"/>
-        <v>17603.189999999999</v>
-      </c>
-      <c r="R61" s="44">
-        <f t="shared" si="19"/>
         <v>0.19</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="60">
         <v>8</v>
       </c>
@@ -7282,47 +7294,47 @@
         <v>4557.2</v>
       </c>
       <c r="I62" s="69">
+        <f t="shared" si="21"/>
+        <v>-133</v>
+      </c>
+      <c r="J62" s="69">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="K62" s="70">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="L62" s="70">
+        <f t="shared" si="14"/>
+        <v>935.76638800000012</v>
+      </c>
+      <c r="M62" s="122">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N62" s="122">
+        <f t="shared" si="25"/>
+        <v>358.96006200000005</v>
+      </c>
+      <c r="O62" s="122">
+        <f t="shared" si="17"/>
+        <v>400</v>
+      </c>
+      <c r="P62" s="71">
+        <f t="shared" si="18"/>
+        <v>1562.2</v>
+      </c>
+      <c r="Q62" s="72">
+        <f t="shared" si="26"/>
+        <v>1609.2</v>
+      </c>
+      <c r="R62" s="44">
         <f t="shared" si="20"/>
-        <v>-133</v>
-      </c>
-      <c r="J62" s="69">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K62" s="70">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L62" s="70">
-        <f t="shared" si="13"/>
-        <v>935.76638800000012</v>
-      </c>
-      <c r="M62" s="122">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N62" s="122">
-        <f t="shared" si="24"/>
-        <v>358.96006200000005</v>
-      </c>
-      <c r="O62" s="122">
-        <f t="shared" si="16"/>
-        <v>400</v>
-      </c>
-      <c r="P62" s="71">
-        <f t="shared" si="17"/>
-        <v>1562.2</v>
-      </c>
-      <c r="Q62" s="72">
-        <f t="shared" si="25"/>
-        <v>1609.2</v>
-      </c>
-      <c r="R62" s="44">
-        <f t="shared" si="19"/>
         <v>0.2</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="60">
         <v>9</v>
       </c>
@@ -7346,47 +7358,47 @@
       </c>
       <c r="H63" s="115"/>
       <c r="I63" s="69">
+        <f t="shared" si="21"/>
+        <v>-42218.79</v>
+      </c>
+      <c r="J63" s="69">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="K63" s="70">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="L63" s="70">
+        <f t="shared" si="14"/>
+        <v>935.76638800000012</v>
+      </c>
+      <c r="M63" s="122">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N63" s="122">
+        <f t="shared" si="25"/>
+        <v>358.96006200000005</v>
+      </c>
+      <c r="O63" s="122">
+        <f t="shared" si="17"/>
+        <v>400</v>
+      </c>
+      <c r="P63" s="71">
+        <f t="shared" si="18"/>
+        <v>-40523.79</v>
+      </c>
+      <c r="Q63" s="72">
+        <f t="shared" si="26"/>
+        <v>-41739.79</v>
+      </c>
+      <c r="R63" s="44">
         <f t="shared" si="20"/>
-        <v>-42218.79</v>
-      </c>
-      <c r="J63" s="69">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K63" s="70">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L63" s="70">
-        <f t="shared" si="13"/>
-        <v>935.76638800000012</v>
-      </c>
-      <c r="M63" s="122">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N63" s="122">
-        <f t="shared" si="24"/>
-        <v>358.96006200000005</v>
-      </c>
-      <c r="O63" s="122">
-        <f t="shared" si="16"/>
-        <v>400</v>
-      </c>
-      <c r="P63" s="71">
-        <f t="shared" si="17"/>
-        <v>-40523.79</v>
-      </c>
-      <c r="Q63" s="72">
-        <f t="shared" si="25"/>
-        <v>-41739.79</v>
-      </c>
-      <c r="R63" s="44">
-        <f t="shared" si="19"/>
         <v>0.21</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="60">
         <v>9</v>
       </c>
@@ -7411,51 +7423,51 @@
         <v>1552.22</v>
       </c>
       <c r="I64" s="69">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="J64" s="69">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="K64" s="70">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="L64" s="70">
+        <f t="shared" si="14"/>
+        <v>935.76638800000012</v>
+      </c>
+      <c r="M64" s="122">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N64" s="122">
+        <f t="shared" si="25"/>
+        <v>358.96006200000005</v>
+      </c>
+      <c r="O64" s="122">
+        <f t="shared" si="17"/>
+        <v>400</v>
+      </c>
+      <c r="P64" s="71">
+        <f t="shared" si="18"/>
+        <v>1695.22</v>
+      </c>
+      <c r="Q64" s="72">
+        <f t="shared" si="26"/>
+        <v>1746.22</v>
+      </c>
+      <c r="R64" s="44">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J64" s="69">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K64" s="70">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L64" s="70">
-        <f t="shared" si="13"/>
-        <v>935.76638800000012</v>
-      </c>
-      <c r="M64" s="122">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N64" s="122">
-        <f t="shared" si="24"/>
-        <v>358.96006200000005</v>
-      </c>
-      <c r="O64" s="122">
-        <f t="shared" si="16"/>
-        <v>400</v>
-      </c>
-      <c r="P64" s="71">
-        <f t="shared" si="17"/>
-        <v>1695.22</v>
-      </c>
-      <c r="Q64" s="72">
-        <f t="shared" si="25"/>
-        <v>1746.22</v>
-      </c>
-      <c r="R64" s="44">
-        <f t="shared" si="19"/>
         <v>0.22</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="60">
         <v>9</v>
       </c>
-      <c r="B65" s="183" t="s">
+      <c r="B65" s="182" t="s">
         <v>210</v>
       </c>
       <c r="C65" s="59">
@@ -7478,47 +7490,47 @@
         <v>1552.23</v>
       </c>
       <c r="I65" s="83">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="J65" s="83">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="K65" s="192">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="L65" s="192">
+        <f t="shared" si="14"/>
+        <v>935.76638800000012</v>
+      </c>
+      <c r="M65" s="193">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N65" s="193">
+        <f t="shared" si="25"/>
+        <v>358.96006200000005</v>
+      </c>
+      <c r="O65" s="193">
+        <f t="shared" si="17"/>
+        <v>400</v>
+      </c>
+      <c r="P65" s="194">
+        <f t="shared" si="18"/>
+        <v>1695.23</v>
+      </c>
+      <c r="Q65" s="195">
+        <f t="shared" si="26"/>
+        <v>1746.23</v>
+      </c>
+      <c r="R65" s="44">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J65" s="83">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K65" s="218">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L65" s="218">
-        <f t="shared" si="13"/>
-        <v>935.76638800000012</v>
-      </c>
-      <c r="M65" s="219">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N65" s="219">
-        <f t="shared" si="24"/>
-        <v>358.96006200000005</v>
-      </c>
-      <c r="O65" s="219">
-        <f t="shared" si="16"/>
-        <v>400</v>
-      </c>
-      <c r="P65" s="220">
-        <f t="shared" si="17"/>
-        <v>1695.23</v>
-      </c>
-      <c r="Q65" s="221">
-        <f t="shared" si="25"/>
-        <v>1746.23</v>
-      </c>
-      <c r="R65" s="44">
-        <f t="shared" si="19"/>
         <v>0.23</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="60">
         <v>10</v>
       </c>
@@ -7543,47 +7555,47 @@
         <v>1599.24</v>
       </c>
       <c r="I66" s="69">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="J66" s="69">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="K66" s="70">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="L66" s="70">
+        <f t="shared" si="14"/>
+        <v>935.76638800000012</v>
+      </c>
+      <c r="M66" s="122">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N66" s="122">
+        <f t="shared" si="25"/>
+        <v>358.96006200000005</v>
+      </c>
+      <c r="O66" s="122">
+        <f t="shared" si="17"/>
+        <v>400</v>
+      </c>
+      <c r="P66" s="71">
+        <f t="shared" si="18"/>
+        <v>1695.24</v>
+      </c>
+      <c r="Q66" s="72">
+        <f t="shared" si="26"/>
+        <v>1746.24</v>
+      </c>
+      <c r="R66" s="44">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J66" s="69">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K66" s="70">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L66" s="70">
-        <f t="shared" si="13"/>
-        <v>935.76638800000012</v>
-      </c>
-      <c r="M66" s="122">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N66" s="122">
-        <f t="shared" si="24"/>
-        <v>358.96006200000005</v>
-      </c>
-      <c r="O66" s="122">
-        <f t="shared" si="16"/>
-        <v>400</v>
-      </c>
-      <c r="P66" s="71">
-        <f t="shared" si="17"/>
-        <v>1695.24</v>
-      </c>
-      <c r="Q66" s="72">
-        <f t="shared" si="25"/>
-        <v>1746.24</v>
-      </c>
-      <c r="R66" s="44">
-        <f t="shared" si="19"/>
         <v>0.24</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="60">
         <v>10</v>
       </c>
@@ -7610,47 +7622,47 @@
         <v>1552.25</v>
       </c>
       <c r="I67" s="69">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="J67" s="69">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="K67" s="70">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="L67" s="70">
+        <f t="shared" si="14"/>
+        <v>935.76638800000012</v>
+      </c>
+      <c r="M67" s="122">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N67" s="122">
+        <f t="shared" si="25"/>
+        <v>358.96006200000005</v>
+      </c>
+      <c r="O67" s="122">
+        <f t="shared" si="17"/>
+        <v>400</v>
+      </c>
+      <c r="P67" s="71">
+        <f t="shared" si="18"/>
+        <v>1695.25</v>
+      </c>
+      <c r="Q67" s="72">
+        <f t="shared" si="26"/>
+        <v>1746.25</v>
+      </c>
+      <c r="R67" s="44">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J67" s="69">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K67" s="70">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L67" s="70">
-        <f t="shared" si="13"/>
-        <v>935.76638800000012</v>
-      </c>
-      <c r="M67" s="122">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N67" s="122">
-        <f t="shared" si="24"/>
-        <v>358.96006200000005</v>
-      </c>
-      <c r="O67" s="122">
-        <f t="shared" si="16"/>
-        <v>400</v>
-      </c>
-      <c r="P67" s="71">
-        <f t="shared" si="17"/>
-        <v>1695.25</v>
-      </c>
-      <c r="Q67" s="72">
-        <f t="shared" si="25"/>
-        <v>1746.25</v>
-      </c>
-      <c r="R67" s="44">
-        <f t="shared" si="19"/>
         <v>0.25</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="60">
         <v>10</v>
       </c>
@@ -7674,47 +7686,47 @@
       </c>
       <c r="H68" s="115"/>
       <c r="I68" s="69">
+        <f t="shared" si="21"/>
+        <v>1552.26</v>
+      </c>
+      <c r="J68" s="69">
+        <f t="shared" si="22"/>
+        <v>46.567799999999998</v>
+      </c>
+      <c r="K68" s="70">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="L68" s="70">
+        <f t="shared" si="14"/>
+        <v>935.76638800000012</v>
+      </c>
+      <c r="M68" s="122">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N68" s="122">
+        <f t="shared" si="25"/>
+        <v>358.96006200000005</v>
+      </c>
+      <c r="O68" s="122">
+        <f t="shared" si="17"/>
+        <v>400</v>
+      </c>
+      <c r="P68" s="71">
+        <f t="shared" si="18"/>
+        <v>3294.26</v>
+      </c>
+      <c r="Q68" s="72">
+        <f t="shared" si="26"/>
+        <v>3393.26</v>
+      </c>
+      <c r="R68" s="44">
         <f t="shared" si="20"/>
-        <v>1552.26</v>
-      </c>
-      <c r="J68" s="69">
-        <f t="shared" si="21"/>
-        <v>46.567799999999998</v>
-      </c>
-      <c r="K68" s="70">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L68" s="70">
-        <f t="shared" si="13"/>
-        <v>935.76638800000012</v>
-      </c>
-      <c r="M68" s="122">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N68" s="122">
-        <f t="shared" si="24"/>
-        <v>358.96006200000005</v>
-      </c>
-      <c r="O68" s="122">
-        <f t="shared" si="16"/>
-        <v>400</v>
-      </c>
-      <c r="P68" s="71">
-        <f t="shared" si="17"/>
-        <v>3294.26</v>
-      </c>
-      <c r="Q68" s="72">
-        <f t="shared" si="25"/>
-        <v>3393.26</v>
-      </c>
-      <c r="R68" s="44">
-        <f t="shared" si="19"/>
         <v>0.26</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="60">
         <v>11</v>
       </c>
@@ -7736,47 +7748,47 @@
       </c>
       <c r="H69" s="115"/>
       <c r="I69" s="69">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>17451.27</v>
       </c>
       <c r="J69" s="69">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>523.53809999999999</v>
       </c>
       <c r="K69" s="70">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="L69" s="70">
-        <f t="shared" ref="L69:L90" si="26">M$1*F69</f>
+        <f t="shared" ref="L69:L90" si="27">M$1*F69</f>
         <v>935.76638800000012</v>
       </c>
       <c r="M69" s="122">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N69" s="122">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>358.96006200000005</v>
       </c>
       <c r="O69" s="122">
-        <f t="shared" ref="O69:O90" si="27">I$2*F69</f>
+        <f t="shared" ref="O69:O90" si="28">I$2*F69</f>
         <v>400</v>
       </c>
       <c r="P69" s="71">
-        <f t="shared" ref="P69:P90" si="28">ROUND(SUM(I69:O69),0) + R69</f>
+        <f t="shared" ref="P69:P90" si="29">ROUND(SUM(I69:O69),0) + R69</f>
         <v>19670.27</v>
       </c>
       <c r="Q69" s="72">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>20260.27</v>
       </c>
       <c r="R69" s="44">
-        <f t="shared" ref="R69:R90" si="29">ROUND(0.001+C69/100,2)</f>
+        <f t="shared" ref="R69:R90" si="30">ROUND(0.001+C69/100,2)</f>
         <v>0.27</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="60">
         <v>11</v>
       </c>
@@ -7798,47 +7810,47 @@
       </c>
       <c r="H70" s="115"/>
       <c r="I70" s="69">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>17451.28</v>
       </c>
       <c r="J70" s="69">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>523.53839999999991</v>
       </c>
       <c r="K70" s="70">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="L70" s="70">
+        <f t="shared" si="27"/>
+        <v>935.76638800000012</v>
+      </c>
+      <c r="M70" s="122">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N70" s="122">
+        <f t="shared" si="25"/>
+        <v>358.96006200000005</v>
+      </c>
+      <c r="O70" s="122">
+        <f t="shared" si="28"/>
+        <v>400</v>
+      </c>
+      <c r="P70" s="71">
+        <f t="shared" si="29"/>
+        <v>19670.28</v>
+      </c>
+      <c r="Q70" s="72">
         <f t="shared" si="26"/>
-        <v>935.76638800000012</v>
-      </c>
-      <c r="M70" s="122">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N70" s="122">
-        <f t="shared" si="24"/>
-        <v>358.96006200000005</v>
-      </c>
-      <c r="O70" s="122">
-        <f t="shared" si="27"/>
-        <v>400</v>
-      </c>
-      <c r="P70" s="71">
-        <f t="shared" si="28"/>
-        <v>19670.28</v>
-      </c>
-      <c r="Q70" s="72">
-        <f t="shared" si="25"/>
         <v>20260.28</v>
       </c>
       <c r="R70" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="60">
         <v>11</v>
       </c>
@@ -7862,47 +7874,47 @@
       </c>
       <c r="H71" s="115"/>
       <c r="I71" s="69">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1552.29</v>
       </c>
       <c r="J71" s="69">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>46.5687</v>
       </c>
       <c r="K71" s="70">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="L71" s="70">
+        <f t="shared" si="27"/>
+        <v>935.76638800000012</v>
+      </c>
+      <c r="M71" s="122">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N71" s="122">
+        <f t="shared" si="25"/>
+        <v>358.96006200000005</v>
+      </c>
+      <c r="O71" s="122">
+        <f t="shared" si="28"/>
+        <v>400</v>
+      </c>
+      <c r="P71" s="71">
+        <f t="shared" si="29"/>
+        <v>3294.29</v>
+      </c>
+      <c r="Q71" s="72">
         <f t="shared" si="26"/>
-        <v>935.76638800000012</v>
-      </c>
-      <c r="M71" s="122">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N71" s="122">
-        <f t="shared" si="24"/>
-        <v>358.96006200000005</v>
-      </c>
-      <c r="O71" s="122">
-        <f t="shared" si="27"/>
-        <v>400</v>
-      </c>
-      <c r="P71" s="71">
-        <f t="shared" si="28"/>
-        <v>3294.29</v>
-      </c>
-      <c r="Q71" s="72">
-        <f t="shared" si="25"/>
         <v>3393.29</v>
       </c>
       <c r="R71" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="60"/>
       <c r="B72" s="76" t="s">
         <v>221</v>
@@ -7924,47 +7936,47 @@
       </c>
       <c r="H72" s="115"/>
       <c r="I72" s="69">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1552.3</v>
       </c>
       <c r="J72" s="69">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>46.568999999999996</v>
       </c>
       <c r="K72" s="70">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="L72" s="70">
+        <f t="shared" si="27"/>
+        <v>935.76638800000012</v>
+      </c>
+      <c r="M72" s="122">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N72" s="122">
+        <f t="shared" si="25"/>
+        <v>358.96006200000005</v>
+      </c>
+      <c r="O72" s="122">
+        <f t="shared" si="28"/>
+        <v>400</v>
+      </c>
+      <c r="P72" s="71">
+        <f t="shared" si="29"/>
+        <v>3294.3</v>
+      </c>
+      <c r="Q72" s="72">
         <f t="shared" si="26"/>
-        <v>935.76638800000012</v>
-      </c>
-      <c r="M72" s="122">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N72" s="122">
-        <f t="shared" si="24"/>
-        <v>358.96006200000005</v>
-      </c>
-      <c r="O72" s="122">
-        <f t="shared" si="27"/>
-        <v>400</v>
-      </c>
-      <c r="P72" s="71">
-        <f t="shared" si="28"/>
-        <v>3294.3</v>
-      </c>
-      <c r="Q72" s="72">
-        <f t="shared" si="25"/>
         <v>3393.3</v>
       </c>
       <c r="R72" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.3</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="60"/>
       <c r="B73" s="76" t="s">
         <v>222</v>
@@ -7984,47 +7996,47 @@
       </c>
       <c r="H73" s="115"/>
       <c r="I73" s="69">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10617.31</v>
       </c>
       <c r="J73" s="69">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>318.51929999999999</v>
       </c>
       <c r="K73" s="70">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="L73" s="70">
+        <f t="shared" si="27"/>
+        <v>935.76638800000012</v>
+      </c>
+      <c r="M73" s="122">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N73" s="122">
+        <f t="shared" si="25"/>
+        <v>358.96006200000005</v>
+      </c>
+      <c r="O73" s="122">
+        <f t="shared" si="28"/>
+        <v>400</v>
+      </c>
+      <c r="P73" s="71">
+        <f t="shared" si="29"/>
+        <v>12631.31</v>
+      </c>
+      <c r="Q73" s="72">
         <f t="shared" si="26"/>
-        <v>935.76638800000012</v>
-      </c>
-      <c r="M73" s="122">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N73" s="122">
-        <f t="shared" si="24"/>
-        <v>358.96006200000005</v>
-      </c>
-      <c r="O73" s="122">
-        <f t="shared" si="27"/>
-        <v>400</v>
-      </c>
-      <c r="P73" s="71">
-        <f t="shared" si="28"/>
-        <v>12631.31</v>
-      </c>
-      <c r="Q73" s="72">
-        <f t="shared" si="25"/>
         <v>13010.31</v>
       </c>
       <c r="R73" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.31</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="60"/>
       <c r="B74" s="76" t="s">
         <v>223</v>
@@ -8044,48 +8056,48 @@
       </c>
       <c r="H74" s="115"/>
       <c r="I74" s="69">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>3100877.32</v>
       </c>
       <c r="J74" s="69">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>93026.319599999988</v>
       </c>
       <c r="K74" s="70">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="L74" s="70">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>73925.544652000011</v>
       </c>
       <c r="M74" s="122">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N74" s="122">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>28357.844898000003</v>
       </c>
       <c r="O74" s="122">
         <v>93376</v>
       </c>
       <c r="P74" s="71">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>3389563.32</v>
       </c>
       <c r="Q74" s="72">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>3491250.32</v>
       </c>
       <c r="R74" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.32</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="60"/>
-      <c r="B75" s="185" t="s">
+      <c r="B75" s="184" t="s">
         <v>225</v>
       </c>
       <c r="C75" s="59">
@@ -8103,49 +8115,49 @@
       </c>
       <c r="H75" s="115"/>
       <c r="I75" s="83">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>449105.01</v>
       </c>
       <c r="J75" s="83">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>13473.150299999999</v>
       </c>
-      <c r="K75" s="218">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L75" s="218">
+      <c r="K75" s="192">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="L75" s="192">
+        <f t="shared" si="27"/>
+        <v>28540.874834000006</v>
+      </c>
+      <c r="M75" s="193">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N75" s="193">
+        <f t="shared" si="25"/>
+        <v>10948.281891000001</v>
+      </c>
+      <c r="O75" s="193">
+        <f t="shared" si="28"/>
+        <v>12200</v>
+      </c>
+      <c r="P75" s="194">
+        <f t="shared" si="29"/>
+        <v>514267.01</v>
+      </c>
+      <c r="Q75" s="195">
         <f t="shared" si="26"/>
-        <v>28540.874834000006</v>
-      </c>
-      <c r="M75" s="219">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N75" s="219">
-        <f t="shared" si="24"/>
-        <v>10948.281891000001</v>
-      </c>
-      <c r="O75" s="219">
-        <f t="shared" si="27"/>
-        <v>12200</v>
-      </c>
-      <c r="P75" s="220">
-        <f t="shared" si="28"/>
-        <v>514267.01</v>
-      </c>
-      <c r="Q75" s="221">
-        <f t="shared" si="25"/>
         <v>529695.01</v>
       </c>
       <c r="R75" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.01</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="60"/>
-      <c r="B76" s="185" t="s">
+      <c r="B76" s="184" t="s">
         <v>226</v>
       </c>
       <c r="C76" s="59">
@@ -8163,49 +8175,49 @@
       </c>
       <c r="H76" s="115"/>
       <c r="I76" s="83">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>49649.02</v>
       </c>
       <c r="J76" s="83">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1489.4705999999999</v>
       </c>
-      <c r="K76" s="218">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L76" s="218">
+      <c r="K76" s="192">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="L76" s="192">
+        <f t="shared" si="27"/>
+        <v>29944.524416000004</v>
+      </c>
+      <c r="M76" s="193">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N76" s="193">
+        <f t="shared" si="25"/>
+        <v>11486.721984000002</v>
+      </c>
+      <c r="O76" s="193">
+        <f t="shared" si="28"/>
+        <v>12800</v>
+      </c>
+      <c r="P76" s="194">
+        <f t="shared" si="29"/>
+        <v>105370.02</v>
+      </c>
+      <c r="Q76" s="195">
         <f t="shared" si="26"/>
-        <v>29944.524416000004</v>
-      </c>
-      <c r="M76" s="219">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N76" s="219">
-        <f t="shared" si="24"/>
-        <v>11486.721984000002</v>
-      </c>
-      <c r="O76" s="219">
-        <f t="shared" si="27"/>
-        <v>12800</v>
-      </c>
-      <c r="P76" s="220">
-        <f t="shared" si="28"/>
-        <v>105370.02</v>
-      </c>
-      <c r="Q76" s="221">
-        <f t="shared" si="25"/>
         <v>108531.02</v>
       </c>
       <c r="R76" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.02</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="60"/>
-      <c r="B77" s="185" t="s">
+      <c r="B77" s="184" t="s">
         <v>228</v>
       </c>
       <c r="C77" s="59">
@@ -8226,49 +8238,49 @@
         <v>44219.03</v>
       </c>
       <c r="I77" s="83">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J77" s="83">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K77" s="218">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L77" s="218">
+      <c r="K77" s="192">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="L77" s="192">
+        <f t="shared" si="27"/>
+        <v>26669.342058000002</v>
+      </c>
+      <c r="M77" s="193">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N77" s="193">
+        <f t="shared" si="25"/>
+        <v>10230.361767</v>
+      </c>
+      <c r="O77" s="193">
+        <f t="shared" si="28"/>
+        <v>11400</v>
+      </c>
+      <c r="P77" s="194">
+        <f t="shared" si="29"/>
+        <v>48300.03</v>
+      </c>
+      <c r="Q77" s="195">
         <f t="shared" si="26"/>
-        <v>26669.342058000002</v>
-      </c>
-      <c r="M77" s="219">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N77" s="219">
-        <f t="shared" si="24"/>
-        <v>10230.361767</v>
-      </c>
-      <c r="O77" s="219">
-        <f t="shared" si="27"/>
-        <v>11400</v>
-      </c>
-      <c r="P77" s="220">
-        <f t="shared" si="28"/>
-        <v>48300.03</v>
-      </c>
-      <c r="Q77" s="221">
-        <f t="shared" si="25"/>
         <v>49749.03</v>
       </c>
       <c r="R77" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.03</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="60"/>
-      <c r="B78" s="185" t="s">
+      <c r="B78" s="184" t="s">
         <v>230</v>
       </c>
       <c r="C78" s="59">
@@ -8289,49 +8301,49 @@
         <v>117248.04</v>
       </c>
       <c r="I78" s="83">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J78" s="83">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K78" s="218">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L78" s="218">
+      <c r="K78" s="192">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="L78" s="192">
+        <f t="shared" si="27"/>
+        <v>24797.809282000002</v>
+      </c>
+      <c r="M78" s="193">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N78" s="193">
+        <f t="shared" si="25"/>
+        <v>9512.4416430000001</v>
+      </c>
+      <c r="O78" s="193">
+        <f t="shared" si="28"/>
+        <v>10600</v>
+      </c>
+      <c r="P78" s="194">
+        <f t="shared" si="29"/>
+        <v>44910.04</v>
+      </c>
+      <c r="Q78" s="195">
         <f t="shared" si="26"/>
-        <v>24797.809282000002</v>
-      </c>
-      <c r="M78" s="219">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N78" s="219">
-        <f t="shared" si="24"/>
-        <v>9512.4416430000001</v>
-      </c>
-      <c r="O78" s="219">
-        <f t="shared" si="27"/>
-        <v>10600</v>
-      </c>
-      <c r="P78" s="220">
-        <f t="shared" si="28"/>
-        <v>44910.04</v>
-      </c>
-      <c r="Q78" s="221">
-        <f t="shared" si="25"/>
         <v>46257.04</v>
       </c>
       <c r="R78" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="60"/>
-      <c r="B79" s="185" t="s">
+      <c r="B79" s="184" t="s">
         <v>231</v>
       </c>
       <c r="C79" s="59">
@@ -8354,49 +8366,49 @@
         <v>41116.050000000003</v>
       </c>
       <c r="I79" s="83">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J79" s="83">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K79" s="218">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L79" s="218">
+      <c r="K79" s="192">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="L79" s="192">
+        <f t="shared" si="27"/>
+        <v>24797.809282000002</v>
+      </c>
+      <c r="M79" s="193">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N79" s="193">
+        <f t="shared" si="25"/>
+        <v>9512.4416430000001</v>
+      </c>
+      <c r="O79" s="193">
+        <f t="shared" si="28"/>
+        <v>10600</v>
+      </c>
+      <c r="P79" s="194">
+        <f t="shared" si="29"/>
+        <v>44910.05</v>
+      </c>
+      <c r="Q79" s="195">
         <f t="shared" si="26"/>
-        <v>24797.809282000002</v>
-      </c>
-      <c r="M79" s="219">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N79" s="219">
-        <f t="shared" si="24"/>
-        <v>9512.4416430000001</v>
-      </c>
-      <c r="O79" s="219">
-        <f t="shared" si="27"/>
-        <v>10600</v>
-      </c>
-      <c r="P79" s="220">
-        <f t="shared" si="28"/>
-        <v>44910.05</v>
-      </c>
-      <c r="Q79" s="221">
-        <f t="shared" si="25"/>
         <v>46257.05</v>
       </c>
       <c r="R79" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="80" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="60"/>
-      <c r="B80" s="185" t="s">
+      <c r="B80" s="184" t="s">
         <v>232</v>
       </c>
       <c r="C80" s="59">
@@ -8419,54 +8431,54 @@
         <v>42349.06</v>
       </c>
       <c r="I80" s="83">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J80" s="83">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K80" s="218">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L80" s="218">
+      <c r="K80" s="192">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="L80" s="192">
+        <f t="shared" si="27"/>
+        <v>24797.809282000002</v>
+      </c>
+      <c r="M80" s="193">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N80" s="193">
+        <f t="shared" si="25"/>
+        <v>9512.4416430000001</v>
+      </c>
+      <c r="O80" s="193">
+        <f t="shared" si="28"/>
+        <v>10600</v>
+      </c>
+      <c r="P80" s="194">
+        <f t="shared" si="29"/>
+        <v>44910.06</v>
+      </c>
+      <c r="Q80" s="195">
         <f t="shared" si="26"/>
-        <v>24797.809282000002</v>
-      </c>
-      <c r="M80" s="219">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N80" s="219">
-        <f t="shared" si="24"/>
-        <v>9512.4416430000001</v>
-      </c>
-      <c r="O80" s="219">
-        <f t="shared" si="27"/>
-        <v>10600</v>
-      </c>
-      <c r="P80" s="220">
-        <f t="shared" si="28"/>
-        <v>44910.06</v>
-      </c>
-      <c r="Q80" s="221">
-        <f t="shared" si="25"/>
         <v>46257.06</v>
       </c>
       <c r="R80" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.06</v>
       </c>
       <c r="S80" s="160" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="60">
         <v>12</v>
       </c>
-      <c r="B81" s="185" t="s">
+      <c r="B81" s="184" t="s">
         <v>235</v>
       </c>
       <c r="C81" s="59">
@@ -8489,51 +8501,51 @@
         <v>41116.07</v>
       </c>
       <c r="I81" s="83">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J81" s="83">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K81" s="218">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L81" s="218">
+      <c r="K81" s="192">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="L81" s="192">
+        <f t="shared" si="27"/>
+        <v>24797.809282000002</v>
+      </c>
+      <c r="M81" s="193">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N81" s="193">
+        <f t="shared" si="25"/>
+        <v>9512.4416430000001</v>
+      </c>
+      <c r="O81" s="193">
+        <f t="shared" si="28"/>
+        <v>10600</v>
+      </c>
+      <c r="P81" s="194">
+        <f t="shared" si="29"/>
+        <v>44910.07</v>
+      </c>
+      <c r="Q81" s="195">
         <f t="shared" si="26"/>
-        <v>24797.809282000002</v>
-      </c>
-      <c r="M81" s="219">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N81" s="219">
-        <f t="shared" si="24"/>
-        <v>9512.4416430000001</v>
-      </c>
-      <c r="O81" s="219">
-        <f t="shared" si="27"/>
-        <v>10600</v>
-      </c>
-      <c r="P81" s="220">
-        <f t="shared" si="28"/>
-        <v>44910.07</v>
-      </c>
-      <c r="Q81" s="221">
-        <f t="shared" si="25"/>
         <v>46257.07</v>
       </c>
       <c r="R81" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="60">
         <v>12</v>
       </c>
-      <c r="B82" s="183" t="s">
+      <c r="B82" s="182" t="s">
         <v>236</v>
       </c>
       <c r="C82" s="59">
@@ -8551,47 +8563,47 @@
       </c>
       <c r="H82" s="115"/>
       <c r="I82" s="83">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>281310.08000000002</v>
       </c>
       <c r="J82" s="83">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>8439.3024000000005</v>
       </c>
-      <c r="K82" s="218">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L82" s="218">
+      <c r="K82" s="192">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="L82" s="192">
+        <f t="shared" si="27"/>
+        <v>24797.809282000002</v>
+      </c>
+      <c r="M82" s="193">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N82" s="193">
+        <f t="shared" si="25"/>
+        <v>9512.4416430000001</v>
+      </c>
+      <c r="O82" s="193">
+        <f t="shared" si="28"/>
+        <v>10600</v>
+      </c>
+      <c r="P82" s="194">
+        <f t="shared" si="29"/>
+        <v>334660.08</v>
+      </c>
+      <c r="Q82" s="195">
         <f t="shared" si="26"/>
-        <v>24797.809282000002</v>
-      </c>
-      <c r="M82" s="219">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N82" s="219">
-        <f t="shared" si="24"/>
-        <v>9512.4416430000001</v>
-      </c>
-      <c r="O82" s="219">
-        <f t="shared" si="27"/>
-        <v>10600</v>
-      </c>
-      <c r="P82" s="220">
-        <f t="shared" si="28"/>
-        <v>334660.08</v>
-      </c>
-      <c r="Q82" s="221">
-        <f t="shared" si="25"/>
         <v>344700.08</v>
       </c>
       <c r="R82" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="60">
         <v>12</v>
       </c>
@@ -8618,47 +8630,47 @@
         <v>156704.09</v>
       </c>
       <c r="I83" s="69">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>51143</v>
       </c>
       <c r="J83" s="69">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1534.29</v>
       </c>
       <c r="K83" s="70">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="L83" s="70">
+        <f t="shared" si="27"/>
+        <v>24797.809282000002</v>
+      </c>
+      <c r="M83" s="122">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N83" s="122">
+        <f t="shared" si="25"/>
+        <v>9512.4416430000001</v>
+      </c>
+      <c r="O83" s="122">
+        <f t="shared" si="28"/>
+        <v>10600</v>
+      </c>
+      <c r="P83" s="71">
+        <f t="shared" si="29"/>
+        <v>97588.09</v>
+      </c>
+      <c r="Q83" s="72">
         <f t="shared" si="26"/>
-        <v>24797.809282000002</v>
-      </c>
-      <c r="M83" s="122">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N83" s="122">
-        <f t="shared" si="24"/>
-        <v>9512.4416430000001</v>
-      </c>
-      <c r="O83" s="122">
-        <f t="shared" si="27"/>
-        <v>10600</v>
-      </c>
-      <c r="P83" s="71">
-        <f t="shared" si="28"/>
-        <v>97588.09</v>
-      </c>
-      <c r="Q83" s="72">
-        <f t="shared" si="25"/>
         <v>100516.09</v>
       </c>
       <c r="R83" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" s="60"/>
       <c r="B84" s="75" t="s">
         <v>238</v>
@@ -8678,52 +8690,52 @@
       </c>
       <c r="H84" s="115"/>
       <c r="I84" s="69">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>386538.1</v>
       </c>
       <c r="J84" s="69">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>11596.142999999998</v>
       </c>
       <c r="K84" s="70">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="L84" s="70">
+        <f t="shared" si="27"/>
+        <v>24797.809282000002</v>
+      </c>
+      <c r="M84" s="122">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N84" s="122">
+        <f t="shared" si="25"/>
+        <v>9512.4416430000001</v>
+      </c>
+      <c r="O84" s="122">
+        <f t="shared" si="28"/>
+        <v>10600</v>
+      </c>
+      <c r="P84" s="71">
+        <f t="shared" si="29"/>
+        <v>443044.1</v>
+      </c>
+      <c r="Q84" s="72">
         <f t="shared" si="26"/>
-        <v>24797.809282000002</v>
-      </c>
-      <c r="M84" s="122">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N84" s="122">
-        <f t="shared" si="24"/>
-        <v>9512.4416430000001</v>
-      </c>
-      <c r="O84" s="122">
-        <f t="shared" si="27"/>
-        <v>10600</v>
-      </c>
-      <c r="P84" s="71">
-        <f t="shared" si="28"/>
-        <v>443044.1</v>
-      </c>
-      <c r="Q84" s="72">
-        <f t="shared" si="25"/>
         <v>456335.1</v>
       </c>
       <c r="R84" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.1</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" s="60"/>
       <c r="B85" s="75" t="s">
         <v>239</v>
       </c>
-      <c r="C85" s="183">
+      <c r="C85" s="182">
         <v>11</v>
       </c>
       <c r="D85" s="59" t="s">
@@ -8732,7 +8744,7 @@
       <c r="E85" s="59" t="s">
         <v>250</v>
       </c>
-      <c r="F85" s="172">
+      <c r="F85" s="171">
         <v>5.3E-3</v>
       </c>
       <c r="G85" s="68">
@@ -8740,47 +8752,47 @@
       </c>
       <c r="H85" s="115"/>
       <c r="I85" s="69">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>170907.11</v>
       </c>
       <c r="J85" s="69">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>5127.2132999999994</v>
       </c>
       <c r="K85" s="70">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="L85" s="70">
+        <f t="shared" si="27"/>
+        <v>24797.809282000002</v>
+      </c>
+      <c r="M85" s="122">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N85" s="122">
+        <f t="shared" si="25"/>
+        <v>9512.4416430000001</v>
+      </c>
+      <c r="O85" s="122">
+        <f t="shared" si="28"/>
+        <v>10600</v>
+      </c>
+      <c r="P85" s="71">
+        <f t="shared" si="29"/>
+        <v>220945.11</v>
+      </c>
+      <c r="Q85" s="72">
         <f t="shared" si="26"/>
-        <v>24797.809282000002</v>
-      </c>
-      <c r="M85" s="122">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N85" s="122">
-        <f t="shared" si="24"/>
-        <v>9512.4416430000001</v>
-      </c>
-      <c r="O85" s="122">
-        <f t="shared" si="27"/>
-        <v>10600</v>
-      </c>
-      <c r="P85" s="71">
-        <f t="shared" si="28"/>
-        <v>220945.11</v>
-      </c>
-      <c r="Q85" s="72">
-        <f t="shared" si="25"/>
         <v>227573.11</v>
       </c>
       <c r="R85" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.11</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" s="60"/>
       <c r="B86" s="75" t="s">
         <v>240</v>
@@ -8805,107 +8817,107 @@
         <v>41116.120000000003</v>
       </c>
       <c r="I86" s="69">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J86" s="69">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="K86" s="70">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="L86" s="70">
+        <f t="shared" si="27"/>
+        <v>24797.809282000002</v>
+      </c>
+      <c r="M86" s="122">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N86" s="122">
+        <f t="shared" si="25"/>
+        <v>9512.4416430000001</v>
+      </c>
+      <c r="O86" s="122">
+        <f t="shared" si="28"/>
+        <v>10600</v>
+      </c>
+      <c r="P86" s="71">
+        <f t="shared" si="29"/>
+        <v>44910.12</v>
+      </c>
+      <c r="Q86" s="72">
+        <f t="shared" si="26"/>
+        <v>46257.120000000003</v>
+      </c>
+      <c r="R86" s="44">
+        <f t="shared" si="30"/>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A87" s="60"/>
+      <c r="B87" s="172" t="s">
+        <v>241</v>
+      </c>
+      <c r="C87" s="172">
+        <v>13</v>
+      </c>
+      <c r="D87" s="180" t="s">
+        <v>139</v>
+      </c>
+      <c r="E87" s="181"/>
+      <c r="F87" s="173">
+        <v>5.3E-3</v>
+      </c>
+      <c r="G87" s="174">
+        <v>41116.129999999997</v>
+      </c>
+      <c r="H87" s="185"/>
+      <c r="I87" s="175">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K86" s="70">
+        <v>41116.129999999997</v>
+      </c>
+      <c r="J87" s="175">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L86" s="70">
+        <v>1233.4838999999999</v>
+      </c>
+      <c r="K87" s="176">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="L87" s="176">
+        <f t="shared" si="27"/>
+        <v>24797.809282000002</v>
+      </c>
+      <c r="M87" s="177">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N87" s="177">
+        <f t="shared" si="25"/>
+        <v>9512.4416430000001</v>
+      </c>
+      <c r="O87" s="177">
+        <f t="shared" si="28"/>
+        <v>10600</v>
+      </c>
+      <c r="P87" s="178">
+        <f t="shared" si="29"/>
+        <v>87260.13</v>
+      </c>
+      <c r="Q87" s="179">
         <f t="shared" si="26"/>
-        <v>24797.809282000002</v>
-      </c>
-      <c r="M86" s="122">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N86" s="122">
-        <f t="shared" si="24"/>
-        <v>9512.4416430000001</v>
-      </c>
-      <c r="O86" s="122">
-        <f t="shared" si="27"/>
-        <v>10600</v>
-      </c>
-      <c r="P86" s="71">
-        <f t="shared" si="28"/>
-        <v>44910.12</v>
-      </c>
-      <c r="Q86" s="72">
-        <f t="shared" si="25"/>
-        <v>46257.120000000003</v>
-      </c>
-      <c r="R86" s="44">
-        <f t="shared" si="29"/>
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A87" s="60"/>
-      <c r="B87" s="173" t="s">
-        <v>241</v>
-      </c>
-      <c r="C87" s="173">
-        <v>13</v>
-      </c>
-      <c r="D87" s="181" t="s">
-        <v>139</v>
-      </c>
-      <c r="E87" s="182"/>
-      <c r="F87" s="174">
-        <v>5.3E-3</v>
-      </c>
-      <c r="G87" s="175">
-        <v>41116.129999999997</v>
-      </c>
-      <c r="H87" s="186"/>
-      <c r="I87" s="176">
-        <f t="shared" si="20"/>
-        <v>41116.129999999997</v>
-      </c>
-      <c r="J87" s="176">
-        <f t="shared" si="21"/>
-        <v>1233.4838999999999</v>
-      </c>
-      <c r="K87" s="177">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L87" s="177">
-        <f t="shared" si="26"/>
-        <v>24797.809282000002</v>
-      </c>
-      <c r="M87" s="178">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N87" s="178">
-        <f t="shared" si="24"/>
-        <v>9512.4416430000001</v>
-      </c>
-      <c r="O87" s="178">
-        <f t="shared" si="27"/>
-        <v>10600</v>
-      </c>
-      <c r="P87" s="179">
-        <f t="shared" si="28"/>
-        <v>87260.13</v>
-      </c>
-      <c r="Q87" s="180">
-        <f t="shared" si="25"/>
         <v>89878.13</v>
       </c>
       <c r="R87" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.13</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="60"/>
       <c r="B88" s="60" t="s">
         <v>242</v>
@@ -8927,47 +8939,47 @@
       </c>
       <c r="H88" s="115"/>
       <c r="I88" s="69">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>41116.14</v>
       </c>
       <c r="J88" s="69">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1233.4841999999999</v>
       </c>
       <c r="K88" s="70">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="L88" s="70">
+        <f t="shared" si="27"/>
+        <v>24797.809282000002</v>
+      </c>
+      <c r="M88" s="122">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N88" s="122">
+        <f t="shared" si="25"/>
+        <v>9512.4416430000001</v>
+      </c>
+      <c r="O88" s="122">
+        <f t="shared" si="28"/>
+        <v>10600</v>
+      </c>
+      <c r="P88" s="71">
+        <f t="shared" si="29"/>
+        <v>87260.14</v>
+      </c>
+      <c r="Q88" s="72">
         <f t="shared" si="26"/>
-        <v>24797.809282000002</v>
-      </c>
-      <c r="M88" s="122">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N88" s="122">
-        <f t="shared" si="24"/>
-        <v>9512.4416430000001</v>
-      </c>
-      <c r="O88" s="122">
-        <f t="shared" si="27"/>
-        <v>10600</v>
-      </c>
-      <c r="P88" s="71">
-        <f t="shared" si="28"/>
-        <v>87260.14</v>
-      </c>
-      <c r="Q88" s="72">
-        <f t="shared" si="25"/>
         <v>89878.14</v>
       </c>
       <c r="R88" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" s="60"/>
       <c r="B89" s="60" t="s">
         <v>244</v>
@@ -8993,47 +9005,47 @@
         <v>41116.15</v>
       </c>
       <c r="I89" s="69">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J89" s="69">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K89" s="70">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="L89" s="70">
+        <f t="shared" si="27"/>
+        <v>24797.809282000002</v>
+      </c>
+      <c r="M89" s="122">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N89" s="122">
+        <f t="shared" si="25"/>
+        <v>9512.4416430000001</v>
+      </c>
+      <c r="O89" s="122">
+        <f t="shared" si="28"/>
+        <v>10600</v>
+      </c>
+      <c r="P89" s="71">
+        <f t="shared" si="29"/>
+        <v>44910.15</v>
+      </c>
+      <c r="Q89" s="72">
         <f t="shared" si="26"/>
-        <v>24797.809282000002</v>
-      </c>
-      <c r="M89" s="122">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N89" s="122">
-        <f t="shared" si="24"/>
-        <v>9512.4416430000001</v>
-      </c>
-      <c r="O89" s="122">
-        <f t="shared" si="27"/>
-        <v>10600</v>
-      </c>
-      <c r="P89" s="71">
-        <f t="shared" si="28"/>
-        <v>44910.15</v>
-      </c>
-      <c r="Q89" s="72">
-        <f t="shared" si="25"/>
         <v>46257.15</v>
       </c>
       <c r="R89" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" s="59"/>
       <c r="B90" s="59" t="s">
         <v>245</v>
@@ -9056,47 +9068,47 @@
         <v>55906.16</v>
       </c>
       <c r="I90" s="142">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J90" s="69">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K90" s="70">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="L90" s="70">
+        <f t="shared" si="27"/>
+        <v>29008.758028</v>
+      </c>
+      <c r="M90" s="122">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="N90" s="122">
+        <f t="shared" si="25"/>
+        <v>11127.761922</v>
+      </c>
+      <c r="O90" s="122">
+        <f t="shared" si="28"/>
+        <v>12400</v>
+      </c>
+      <c r="P90" s="71">
+        <f t="shared" si="29"/>
+        <v>52537.16</v>
+      </c>
+      <c r="Q90" s="72">
         <f t="shared" si="26"/>
-        <v>29008.758028</v>
-      </c>
-      <c r="M90" s="122">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N90" s="122">
-        <f t="shared" si="24"/>
-        <v>11127.761922</v>
-      </c>
-      <c r="O90" s="122">
-        <f t="shared" si="27"/>
-        <v>12400</v>
-      </c>
-      <c r="P90" s="71">
-        <f t="shared" si="28"/>
-        <v>52537.16</v>
-      </c>
-      <c r="Q90" s="72">
-        <f t="shared" si="25"/>
         <v>54113.16</v>
       </c>
       <c r="R90" s="44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="60"/>
       <c r="B91" s="132"/>
       <c r="C91" s="132"/>
@@ -9104,7 +9116,7 @@
       <c r="E91" s="132"/>
       <c r="F91" s="143"/>
       <c r="G91" s="144"/>
-      <c r="H91" s="187"/>
+      <c r="H91" s="186"/>
       <c r="I91" s="145"/>
       <c r="J91" s="146"/>
       <c r="K91" s="147"/>
@@ -9116,38 +9128,38 @@
       <c r="Q91" s="149"/>
       <c r="R91" s="44"/>
     </row>
-    <row r="92" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="79"/>
       <c r="B92" s="150"/>
       <c r="C92" s="151"/>
       <c r="D92" s="152"/>
       <c r="E92" s="152"/>
       <c r="F92" s="153">
-        <f t="shared" ref="F92:L92" si="30">SUM(F5:F91)</f>
+        <f t="shared" ref="F92:L92" si="31">SUM(F5:F91)</f>
         <v>0.99999999999999956</v>
       </c>
       <c r="G92" s="154">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>15134186.799999999</v>
       </c>
       <c r="H92" s="155">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>6764876.5000000009</v>
       </c>
       <c r="I92" s="156">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>8369310.299999998</v>
       </c>
       <c r="J92" s="157">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>252632.58240000001</v>
       </c>
       <c r="K92" s="157">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="L92" s="158">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>4678831.9400000013</v>
       </c>
       <c r="M92" s="158">
@@ -9171,213 +9183,216 @@
         <v>17672108.699999996</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D93" s="50"/>
       <c r="E93" s="50"/>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D94" s="217" t="s">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D94" s="249" t="s">
         <v>252</v>
       </c>
-      <c r="E94" s="217"/>
-      <c r="F94" s="217"/>
-      <c r="G94" s="217"/>
-      <c r="H94" s="217"/>
-      <c r="I94" s="217"/>
-      <c r="J94" s="217"/>
-      <c r="K94" s="217"/>
-      <c r="L94" s="217"/>
-      <c r="M94" s="217"/>
-      <c r="N94" s="217"/>
-      <c r="O94" s="217"/>
-      <c r="P94" s="217"/>
-    </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D95" s="217"/>
-      <c r="E95" s="217"/>
-      <c r="F95" s="217"/>
-      <c r="G95" s="217"/>
-      <c r="H95" s="217"/>
-      <c r="I95" s="217"/>
-      <c r="J95" s="217"/>
-      <c r="K95" s="217"/>
-      <c r="L95" s="217"/>
-      <c r="M95" s="217"/>
-      <c r="N95" s="217"/>
-      <c r="O95" s="217"/>
-      <c r="P95" s="217"/>
-    </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="E94" s="249"/>
+      <c r="F94" s="249"/>
+      <c r="G94" s="249"/>
+      <c r="H94" s="249"/>
+      <c r="I94" s="249"/>
+      <c r="J94" s="249"/>
+      <c r="K94" s="249"/>
+      <c r="L94" s="249"/>
+      <c r="M94" s="249"/>
+      <c r="N94" s="249"/>
+      <c r="O94" s="249"/>
+      <c r="P94" s="249"/>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D95" s="249"/>
+      <c r="E95" s="249"/>
+      <c r="F95" s="249"/>
+      <c r="G95" s="249"/>
+      <c r="H95" s="249"/>
+      <c r="I95" s="249"/>
+      <c r="J95" s="249"/>
+      <c r="K95" s="249"/>
+      <c r="L95" s="249"/>
+      <c r="M95" s="249"/>
+      <c r="N95" s="249"/>
+      <c r="O95" s="249"/>
+      <c r="P95" s="249"/>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="H96" s="116"/>
     </row>
-    <row r="97" spans="4:16" x14ac:dyDescent="0.25">
-      <c r="D97" s="271" t="s">
-        <v>276</v>
-      </c>
-      <c r="E97" s="271"/>
-      <c r="F97" s="271"/>
-      <c r="G97" s="271"/>
-      <c r="H97" s="271"/>
-      <c r="I97" s="271"/>
-      <c r="J97" s="271"/>
-      <c r="K97" s="271"/>
-      <c r="L97" s="271"/>
-      <c r="M97" s="271"/>
-      <c r="N97" s="271"/>
-      <c r="O97" s="271"/>
-      <c r="P97" s="271"/>
-    </row>
-    <row r="98" spans="4:16" x14ac:dyDescent="0.25">
-      <c r="D98" s="271"/>
-      <c r="E98" s="271"/>
-      <c r="F98" s="271"/>
-      <c r="G98" s="271"/>
-      <c r="H98" s="271"/>
-      <c r="I98" s="271"/>
-      <c r="J98" s="271"/>
-      <c r="K98" s="271"/>
-      <c r="L98" s="271"/>
-      <c r="M98" s="271"/>
-      <c r="N98" s="271"/>
-      <c r="O98" s="271"/>
-      <c r="P98" s="271"/>
-    </row>
-    <row r="99" spans="4:16" x14ac:dyDescent="0.25">
-      <c r="D99" s="271"/>
-      <c r="E99" s="271"/>
-      <c r="F99" s="271"/>
-      <c r="G99" s="271"/>
-      <c r="H99" s="271"/>
-      <c r="I99" s="271"/>
-      <c r="J99" s="271"/>
-      <c r="K99" s="271"/>
-      <c r="L99" s="271"/>
-      <c r="M99" s="271"/>
-      <c r="N99" s="271"/>
-      <c r="O99" s="271"/>
-      <c r="P99" s="271"/>
-    </row>
-    <row r="100" spans="4:16" x14ac:dyDescent="0.25">
-      <c r="D100" s="271"/>
-      <c r="E100" s="271"/>
-      <c r="F100" s="271"/>
-      <c r="G100" s="271"/>
-      <c r="H100" s="271"/>
-      <c r="I100" s="271"/>
-      <c r="J100" s="271"/>
-      <c r="K100" s="271"/>
-      <c r="L100" s="271"/>
-      <c r="M100" s="271"/>
-      <c r="N100" s="271"/>
-      <c r="O100" s="271"/>
-      <c r="P100" s="271"/>
-    </row>
-    <row r="101" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D97" s="258" t="s">
+        <v>274</v>
+      </c>
+      <c r="E97" s="258"/>
+      <c r="F97" s="258"/>
+      <c r="G97" s="258"/>
+      <c r="H97" s="258"/>
+      <c r="I97" s="258"/>
+      <c r="J97" s="258"/>
+      <c r="K97" s="258"/>
+      <c r="L97" s="258"/>
+      <c r="M97" s="258"/>
+      <c r="N97" s="258"/>
+      <c r="O97" s="258"/>
+      <c r="P97" s="258"/>
+    </row>
+    <row r="98" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D98" s="258"/>
+      <c r="E98" s="258"/>
+      <c r="F98" s="258"/>
+      <c r="G98" s="258"/>
+      <c r="H98" s="258"/>
+      <c r="I98" s="258"/>
+      <c r="J98" s="258"/>
+      <c r="K98" s="258"/>
+      <c r="L98" s="258"/>
+      <c r="M98" s="258"/>
+      <c r="N98" s="258"/>
+      <c r="O98" s="258"/>
+      <c r="P98" s="258"/>
+    </row>
+    <row r="99" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D99" s="258"/>
+      <c r="E99" s="258"/>
+      <c r="F99" s="258"/>
+      <c r="G99" s="258"/>
+      <c r="H99" s="258"/>
+      <c r="I99" s="258"/>
+      <c r="J99" s="258"/>
+      <c r="K99" s="258"/>
+      <c r="L99" s="258"/>
+      <c r="M99" s="258"/>
+      <c r="N99" s="258"/>
+      <c r="O99" s="258"/>
+      <c r="P99" s="258"/>
+    </row>
+    <row r="100" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D100" s="258"/>
+      <c r="E100" s="258"/>
+      <c r="F100" s="258"/>
+      <c r="G100" s="258"/>
+      <c r="H100" s="258"/>
+      <c r="I100" s="258"/>
+      <c r="J100" s="258"/>
+      <c r="K100" s="258"/>
+      <c r="L100" s="258"/>
+      <c r="M100" s="258"/>
+      <c r="N100" s="258"/>
+      <c r="O100" s="258"/>
+      <c r="P100" s="258"/>
+    </row>
+    <row r="101" spans="4:16" x14ac:dyDescent="0.3">
       <c r="H101" s="116"/>
     </row>
-    <row r="102" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:16" x14ac:dyDescent="0.3">
       <c r="H102" s="116"/>
     </row>
-    <row r="103" spans="4:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D103" s="202" t="str">
+    <row r="103" spans="4:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D103" s="219" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, LES PEDIMOS ENCARECIDAMENTE QUE RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. IMPORTANTE PARA DUEÑOS O INQUILINOS DE DEPARTAMENTOS O COCHERAS: QUEREMOS RECORDARLES UNA CUESTIÓN IMPORTANTE RESPECTO A LOS PAGOS DE EXPENSAS, QUE AYUDA A EVITAR ERRORES EN LA IMPUTACIÓN DE LOS MISMOS. EL SISTEMA QUE UTILIZAMOS ASIGNA CENTAVOS ÚNICOS A CADA UNIDAD FUNCIONAL (UF), LO CUAL NOS PERMITE IDENTIFICAR AUTOMÁTICAMENTE A QUÉ UNIDAD CORRESPONDE CADA TRANSFERENCIA. ES DECIR, CADA UF TIENE UN NÚMERO ESPECÍFICO DE CENTAVOS QUE ACTÚA COMO "IDENTIFICADOR". POR EJEMPLO, SI TU UF ES LA 45, EL IMPORTE A ABONAR DEBERÍA TERMINAR EN $...,45. SI TENÉS MÁS DE UNA UNIDAD (POR EJEMPLO, UN DEPARTAMENTO Y UNA COCHERA), CADA UNA TIENE SU PROPIO CÓDIGO DE CENTAVOS. EN ESOS CASOS, TE PEDIMOS POR FAVOR QUE REALICES UNA TRANSFERENCIA POR CADA UF, RESPETANDO EL IMPORTE CON SUS CENTAVOS CORRESPONDIENTES. SABEMOS QUE A VECES, POR COMODIDAD, SE SUELE ENVIAR TODO JUNTO EN UNA SOLA TRANSFERENCIA, PERO ESTO PUEDE GENERAR CONFUSIÓN O ERRORES EN LA IMPUTACIÓN AUTOMÁTICA. REALIZAR LOS PAGOS POR SEPARADO NOS PERMITE ASEGURAR QUE CADA IMPORTE SE ASIGNE CORRECTAMENTE. AGRADECEMOS MUCHÍSIMO LA COLABORACIÓN PARA SEGUIR MANTENIENDO TODO ORDENADO. SALUDOS CORDIALES.</v>
       </c>
-      <c r="E103" s="197"/>
-      <c r="F103" s="197"/>
-      <c r="G103" s="197"/>
-      <c r="H103" s="197"/>
-      <c r="I103" s="197"/>
-      <c r="J103" s="197"/>
-      <c r="K103" s="197"/>
-      <c r="L103" s="197"/>
-      <c r="M103" s="197"/>
-      <c r="N103" s="197"/>
-      <c r="O103" s="197"/>
-      <c r="P103" s="197"/>
-    </row>
-    <row r="104" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D104" s="197"/>
-      <c r="E104" s="197"/>
-      <c r="F104" s="197"/>
-      <c r="G104" s="197"/>
-      <c r="H104" s="197"/>
-      <c r="I104" s="197"/>
-      <c r="J104" s="197"/>
-      <c r="K104" s="197"/>
-      <c r="L104" s="197"/>
-      <c r="M104" s="197"/>
-      <c r="N104" s="197"/>
-      <c r="O104" s="197"/>
-      <c r="P104" s="197"/>
-    </row>
-    <row r="105" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D105" s="197"/>
-      <c r="E105" s="197"/>
-      <c r="F105" s="197"/>
-      <c r="G105" s="197"/>
-      <c r="H105" s="197"/>
-      <c r="I105" s="197"/>
-      <c r="J105" s="197"/>
-      <c r="K105" s="197"/>
-      <c r="L105" s="197"/>
-      <c r="M105" s="197"/>
-      <c r="N105" s="197"/>
-      <c r="O105" s="197"/>
-      <c r="P105" s="197"/>
-    </row>
-    <row r="106" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D106" s="197"/>
-      <c r="E106" s="197"/>
-      <c r="F106" s="197"/>
-      <c r="G106" s="197"/>
-      <c r="H106" s="197"/>
-      <c r="I106" s="197"/>
-      <c r="J106" s="197"/>
-      <c r="K106" s="197"/>
-      <c r="L106" s="197"/>
-      <c r="M106" s="197"/>
-      <c r="N106" s="197"/>
-      <c r="O106" s="197"/>
-      <c r="P106" s="197"/>
-    </row>
-    <row r="107" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D107" s="197"/>
-      <c r="E107" s="197"/>
-      <c r="F107" s="197"/>
-      <c r="G107" s="197"/>
-      <c r="H107" s="197"/>
-      <c r="I107" s="197"/>
-      <c r="J107" s="197"/>
-      <c r="K107" s="197"/>
-      <c r="L107" s="197"/>
-      <c r="M107" s="197"/>
-      <c r="N107" s="197"/>
-      <c r="O107" s="197"/>
-      <c r="P107" s="197"/>
-    </row>
-    <row r="108" spans="4:16" ht="147" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D108" s="197"/>
-      <c r="E108" s="197"/>
-      <c r="F108" s="197"/>
-      <c r="G108" s="197"/>
-      <c r="H108" s="197"/>
-      <c r="I108" s="197"/>
-      <c r="J108" s="197"/>
-      <c r="K108" s="197"/>
-      <c r="L108" s="197"/>
-      <c r="M108" s="197"/>
-      <c r="N108" s="197"/>
-      <c r="O108" s="197"/>
-      <c r="P108" s="197"/>
+      <c r="E103" s="220"/>
+      <c r="F103" s="220"/>
+      <c r="G103" s="220"/>
+      <c r="H103" s="220"/>
+      <c r="I103" s="220"/>
+      <c r="J103" s="220"/>
+      <c r="K103" s="220"/>
+      <c r="L103" s="220"/>
+      <c r="M103" s="220"/>
+      <c r="N103" s="220"/>
+      <c r="O103" s="220"/>
+      <c r="P103" s="220"/>
+    </row>
+    <row r="104" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D104" s="220"/>
+      <c r="E104" s="220"/>
+      <c r="F104" s="220"/>
+      <c r="G104" s="220"/>
+      <c r="H104" s="220"/>
+      <c r="I104" s="220"/>
+      <c r="J104" s="220"/>
+      <c r="K104" s="220"/>
+      <c r="L104" s="220"/>
+      <c r="M104" s="220"/>
+      <c r="N104" s="220"/>
+      <c r="O104" s="220"/>
+      <c r="P104" s="220"/>
+    </row>
+    <row r="105" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D105" s="220"/>
+      <c r="E105" s="220"/>
+      <c r="F105" s="220"/>
+      <c r="G105" s="220"/>
+      <c r="H105" s="220"/>
+      <c r="I105" s="220"/>
+      <c r="J105" s="220"/>
+      <c r="K105" s="220"/>
+      <c r="L105" s="220"/>
+      <c r="M105" s="220"/>
+      <c r="N105" s="220"/>
+      <c r="O105" s="220"/>
+      <c r="P105" s="220"/>
+    </row>
+    <row r="106" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D106" s="220"/>
+      <c r="E106" s="220"/>
+      <c r="F106" s="220"/>
+      <c r="G106" s="220"/>
+      <c r="H106" s="220"/>
+      <c r="I106" s="220"/>
+      <c r="J106" s="220"/>
+      <c r="K106" s="220"/>
+      <c r="L106" s="220"/>
+      <c r="M106" s="220"/>
+      <c r="N106" s="220"/>
+      <c r="O106" s="220"/>
+      <c r="P106" s="220"/>
+    </row>
+    <row r="107" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D107" s="220"/>
+      <c r="E107" s="220"/>
+      <c r="F107" s="220"/>
+      <c r="G107" s="220"/>
+      <c r="H107" s="220"/>
+      <c r="I107" s="220"/>
+      <c r="J107" s="220"/>
+      <c r="K107" s="220"/>
+      <c r="L107" s="220"/>
+      <c r="M107" s="220"/>
+      <c r="N107" s="220"/>
+      <c r="O107" s="220"/>
+      <c r="P107" s="220"/>
+    </row>
+    <row r="108" spans="4:16" ht="147" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D108" s="220"/>
+      <c r="E108" s="220"/>
+      <c r="F108" s="220"/>
+      <c r="G108" s="220"/>
+      <c r="H108" s="220"/>
+      <c r="I108" s="220"/>
+      <c r="J108" s="220"/>
+      <c r="K108" s="220"/>
+      <c r="L108" s="220"/>
+      <c r="M108" s="220"/>
+      <c r="N108" s="220"/>
+      <c r="O108" s="220"/>
+      <c r="P108" s="220"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="D94:P95"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="D103:P108"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H3:H4"/>
@@ -9386,20 +9401,17 @@
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="D97:P100"/>
-    <mergeCell ref="M1:N1"/>
     <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="L3:L4"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="N3:N4"/>
-    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="D94:P95"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -9408,59 +9420,92 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8AEA40-856C-4C69-BDF8-B1FFAA30BA95}">
-  <dimension ref="D3:I21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="D3:J21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D3" s="116"/>
     </row>
-    <row r="4" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D4" s="116"/>
     </row>
-    <row r="5" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D5" s="116"/>
     </row>
-    <row r="6" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D6" s="116"/>
     </row>
-    <row r="7" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D7" s="116"/>
     </row>
-    <row r="8" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D8" s="164" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="9" spans="4:9" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="9" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D9" s="116"/>
     </row>
-    <row r="10" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D10" s="116"/>
     </row>
-    <row r="11" spans="4:9" ht="67.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="4:10" ht="67.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D12" s="116"/>
     </row>
-    <row r="13" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D13" s="116"/>
-    </row>
-    <row r="14" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="E13" s="116"/>
+      <c r="F13" s="116"/>
+      <c r="G13" s="116"/>
+      <c r="H13" s="116"/>
+      <c r="I13" s="116"/>
+      <c r="J13" s="116"/>
+    </row>
+    <row r="14" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D14" s="116"/>
-    </row>
-    <row r="15" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D15" s="165" t="s">
-        <v>254</v>
-      </c>
-      <c r="E15" s="165"/>
-      <c r="F15" s="165"/>
-      <c r="G15" s="165"/>
-      <c r="H15" s="165"/>
-      <c r="I15" s="165"/>
-    </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="E14" s="116"/>
+      <c r="F14" s="116"/>
+      <c r="G14" s="116"/>
+      <c r="H14" s="116"/>
+      <c r="I14" s="116"/>
+      <c r="J14" s="116"/>
+    </row>
+    <row r="15" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+      <c r="G15" s="116"/>
+      <c r="H15" s="116"/>
+      <c r="I15" s="116"/>
+      <c r="J15" s="116"/>
+    </row>
+    <row r="16" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="E16" s="116"/>
+      <c r="F16" s="116"/>
+      <c r="G16" s="116"/>
+      <c r="H16" s="116"/>
+      <c r="I16" s="116"/>
+      <c r="J16" s="116"/>
+    </row>
+    <row r="17" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="E17" s="116"/>
+      <c r="F17" s="116"/>
+      <c r="G17" s="116"/>
+      <c r="H17" s="116"/>
+      <c r="I17" s="116"/>
+      <c r="J17" s="116"/>
+    </row>
+    <row r="18" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D18" s="116"/>
-    </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="116"/>
+      <c r="I18" s="116"/>
+      <c r="J18" s="116"/>
+    </row>
+    <row r="21" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D21" s="116"/>
       <c r="E21" s="116"/>
       <c r="F21" s="116"/>
